--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>AGN.AS</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>36.8</v>
+        <v>45.2</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>21.8</v>
+        <v>30.2</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -822,7 +822,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>3</v>
@@ -831,13 +831,13 @@
         <v>6</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0177</v>
+        <v>0.0248</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>ASRNL.AS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>35</v>
+        <v>39.2</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>20</v>
+        <v>24.2</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -870,25 +870,25 @@
         <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0186</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>HEIA.AS</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>32.4</v>
+        <v>39.2</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>17.4</v>
+        <v>24.2</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -924,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
@@ -933,13 +933,13 @@
         <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0237</v>
+        <v>0.0146</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>32</v>
+        <v>39.2</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>17</v>
+        <v>24.2</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0369</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>VPK.AS</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>31.4</v>
+        <v>38.6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16.4</v>
+        <v>23.6</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0141</v>
+        <v>0.0278</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>AKZA.AS</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>30.6</v>
+        <v>36.2</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>15.6</v>
+        <v>21.2</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>2.4</v>
@@ -1092,7 +1092,7 @@
         <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0582</v>
+        <v>0.0203</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29.6</v>
+        <v>36</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>14.6</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1128,22 +1128,22 @@
         <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.0191</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>29</v>
+        <v>34.4</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>14</v>
+        <v>19.4</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1182,19 +1182,19 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.015</v>
+        <v>0.0183</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>UNA.AS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>28.2</v>
+        <v>33.6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13.2</v>
+        <v>18.6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1233,19 +1233,19 @@
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.0479</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>26.6</v>
+        <v>33</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>11.6</v>
+        <v>18</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1284,19 +1284,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0189</v>
+        <v>0.032</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>ML.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>26.4</v>
+        <v>32.6</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1335,19 +1335,19 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0173</v>
+        <v>0.0215</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>26.4</v>
+        <v>32.6</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,25 +1380,25 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0152</v>
+        <v>0.0272</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>UMG.AS</t>
+          <t>AI.PA</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>26.4</v>
+        <v>32</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>11.4</v>
+        <v>17</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1440,16 +1440,16 @@
         <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.0179</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RI.PA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>26</v>
+        <v>31.4</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>11</v>
+        <v>16.4</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1482,25 +1482,25 @@
         <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.027</v>
+        <v>0.0329</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25.2</v>
+        <v>31.4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>10.2</v>
+        <v>16.4</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1533,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0259</v>
+        <v>0.0302</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>AD.AS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>22.4</v>
+        <v>30.8</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>7.4</v>
+        <v>15.8</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>0</v>
@@ -1602,12 +1602,2358 @@
         <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0317</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CA.PA</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>AIR.PA</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>BNP.PA</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>CS.PA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>BN.PA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>RMS.PA</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>0941.HK</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>EN.PA</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>ENGI.PA</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>9999.HK</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>ACA.PA</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>MC.PA</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>LR.PA</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>0388.HK</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>EL.PA</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>2318.HK</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>0027.HK</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>ORA.PA</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>1398.HK</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>0016.HK</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>0002.HK</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M63" s="9" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1728,7 +4074,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-06T16:03:21.901073</t>
+          <t>2026-06-07T07:24:11.962795</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0179</v>
+        <v>0.0329</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,7 +1463,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1482,25 +1482,25 @@
         <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0329</v>
+        <v>0.0302</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1533,11 +1533,11 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0302</v>
+        <v>0.0317</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,7 +1565,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1584,25 +1584,25 @@
         <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M17" s="9" t="n">
-        <v>0.0317</v>
+        <v>0.0181</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1647,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0181</v>
+        <v>0.0321</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,16 +1686,16 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K19" s="8" t="n">
         <v>3.2</v>
@@ -1704,7 +1704,7 @@
         <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0321</v>
+        <v>0.0209</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -1740,22 +1740,22 @@
         <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0217</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>30.2</v>
+        <v>29.6</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1788,25 +1788,25 @@
         <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0217</v>
+        <v>0.0325</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,7 +1820,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -1839,16 +1839,16 @@
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>5.6</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.0207</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,7 +1871,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0207</v>
+        <v>0.025</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1941,25 +1941,25 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0299</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0299</v>
+        <v>0.015</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>29</v>
+        <v>28.4</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>3.2</v>
@@ -2061,7 +2061,7 @@
         <v>1.8</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.015</v>
+        <v>0.0275</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2094,25 +2094,25 @@
         <v>0</v>
       </c>
       <c r="G27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
         <v>2.4</v>
       </c>
-      <c r="H27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K27" s="8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L27" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0275</v>
+        <v>0.0231</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,7 +2126,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -2163,7 +2163,7 @@
         <v>4.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0231</v>
+        <v>0.0364</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,7 +2177,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -2205,16 +2205,16 @@
         <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0364</v>
+        <v>0.022</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2247,25 +2247,25 @@
         <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.022</v>
+        <v>0.0208</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>28</v>
+        <v>27.4</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2298,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>6</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0208</v>
+        <v>0.02</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>27.4</v>
+        <v>26.8</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2349,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>4</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0241</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2400,25 +2400,25 @@
         <v>0</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0241</v>
+        <v>0.0189</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>RMS.PA</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0343</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,7 +2483,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0343</v>
+        <v>0.0229</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,7 +2534,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0229</v>
+        <v>0.0179</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,7 +2585,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>0</v>
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0125</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2655,25 +2655,25 @@
         <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L38" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0125</v>
+        <v>0.0173</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0173</v>
+        <v>0.0152</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,7 +2738,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>2.4</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.0384</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2814,19 +2814,19 @@
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0384</v>
+        <v>0.0209</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,7 +2840,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -2859,25 +2859,25 @@
         <v>0</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0301</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,7 +2891,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0301</v>
+        <v>0.0307</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,7 +2942,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0307</v>
+        <v>0.0225</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3012,25 +3012,25 @@
         <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K45" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0225</v>
+        <v>0.0267</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>0</v>
@@ -3072,13 +3072,13 @@
         <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M46" s="6" t="n">
         <v>0.0267</v>
@@ -3095,7 +3095,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -3132,7 +3132,7 @@
         <v>4.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0182</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>EL.PA</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3165,25 +3165,25 @@
         <v>0</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L48" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0182</v>
+        <v>0.0259</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0259</v>
+        <v>0.0291</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,7 +3248,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -3285,7 +3285,7 @@
         <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.0212</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
@@ -3333,10 +3333,10 @@
         <v>3.2</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0212</v>
+        <v>0.0271</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,7 +3350,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -3387,7 +3387,7 @@
         <v>3.6</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0271</v>
+        <v>0.0263</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,14 +3401,14 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>15</v>
@@ -3420,25 +3420,25 @@
         <v>0</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.03</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3471,25 +3471,25 @@
         <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.03</v>
+        <v>0.0165</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,7 +3503,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
@@ -3534,13 +3534,13 @@
         <v>0</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L55" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0165</v>
+        <v>0.0278</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,7 +3554,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>0</v>
@@ -3588,10 +3588,10 @@
         <v>2.4</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0278</v>
+        <v>0.0197</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.0167</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>0</v>
@@ -3687,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0167</v>
+        <v>0.0133</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,7 +3707,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -3744,7 +3744,7 @@
         <v>3.6</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.0318</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,14 +3758,14 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>15</v>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H60" s="5" t="n">
         <v>0</v>
@@ -3789,13 +3789,13 @@
         <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0318</v>
+        <v>0.0264</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,14 +3809,14 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>15</v>
@@ -3828,25 +3828,25 @@
         <v>0</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="L61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0264</v>
+        <v>0.0228</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
@@ -3860,14 +3860,14 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>15</v>
@@ -3879,81 +3879,30 @@
         <v>0</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0228</v>
+        <v>0.0174</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>0002.HK</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C63" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M63" s="9" t="n">
-        <v>0.0174</v>
-      </c>
-      <c r="N63" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" s="8" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -4074,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-07T07:24:11.962795</t>
+          <t>2026-06-07T19:01:46.236347</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1077,13 +1077,13 @@
         <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>2.4</v>
@@ -1092,7 +1092,7 @@
         <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0203</v>
+        <v>0.0191</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>21</v>
+        <v>19.4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1128,7 +1128,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>3</v>
@@ -1137,13 +1137,13 @@
         <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0191</v>
+        <v>0.0183</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>34.4</v>
+        <v>33.6</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>19.4</v>
+        <v>18.6</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1185,16 +1185,16 @@
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0479</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1236,16 +1236,16 @@
         <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0479</v>
+        <v>0.032</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ML.PA</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1290,13 +1290,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.032</v>
+        <v>0.0215</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
@@ -1341,13 +1341,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0272</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>32.6</v>
+        <v>31.4</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17.6</v>
+        <v>16.4</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
@@ -1389,16 +1389,16 @@
         <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0272</v>
+        <v>0.0329</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,25 +1431,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0329</v>
+        <v>0.0317</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>31.4</v>
+        <v>30.8</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1482,25 +1482,25 @@
         <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L15" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M15" s="9" t="n">
-        <v>0.0302</v>
+        <v>0.0181</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,7 +1514,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1536,10 +1536,10 @@
         <v>6</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -1548,10 +1548,10 @@
         <v>3.2</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0317</v>
+        <v>0.0321</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1590,19 +1590,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0181</v>
+        <v>0.0209</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1635,13 +1635,13 @@
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>3.2</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.0217</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>30.2</v>
+        <v>29.6</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
@@ -1695,16 +1695,16 @@
         <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0209</v>
+        <v>0.0325</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>30.2</v>
+        <v>29.6</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15.2</v>
+        <v>14.6</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1737,25 +1737,25 @@
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0217</v>
+        <v>0.0207</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1788,16 +1788,16 @@
         <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>5.6</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0325</v>
+        <v>0.025</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1839,25 +1839,25 @@
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0207</v>
+        <v>0.0299</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>29.6</v>
+        <v>29</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1890,25 +1890,25 @@
         <v>0</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="K23" s="8" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1941,25 +1941,25 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0299</v>
+        <v>0.0205</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>29</v>
+        <v>28.4</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K25" s="8" t="n">
         <v>3.2</v>
@@ -2010,7 +2010,7 @@
         <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.015</v>
+        <v>0.0275</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2043,25 +2043,25 @@
         <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L26" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0275</v>
+        <v>0.0231</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,7 +2075,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -2112,7 +2112,7 @@
         <v>4.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0231</v>
+        <v>0.0374</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,7 +2126,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0</v>
@@ -2157,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0312</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2585,7 +2585,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>0</v>
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0125</v>
+        <v>0.0201</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,7 +2636,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -2655,25 +2655,25 @@
         <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0173</v>
+        <v>0.0198</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0152</v>
+        <v>0.0173</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,7 +2738,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>2.4</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0384</v>
+        <v>0.0152</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>0</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0267</v>
+        <v>0.0142</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>0</v>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0182</v>
+        <v>0.0314</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>0</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0259</v>
+        <v>0.0267</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>EL.PA</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0291</v>
+        <v>0.0259</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,7 +3248,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -3285,7 +3285,7 @@
         <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0212</v>
+        <v>0.0291</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
@@ -3333,10 +3333,10 @@
         <v>3.2</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0271</v>
+        <v>0.0214</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,7 +3350,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -3387,7 +3387,7 @@
         <v>3.6</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0263</v>
+        <v>0.0271</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,14 +3401,14 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>15</v>
@@ -3420,25 +3420,25 @@
         <v>0</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.03</v>
+        <v>0.0126</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3471,25 +3471,25 @@
         <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0165</v>
+        <v>0.03</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,7 +3503,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
@@ -3534,13 +3534,13 @@
         <v>0</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0278</v>
+        <v>0.0165</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,7 +3554,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>0</v>
@@ -3588,10 +3588,10 @@
         <v>2.4</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0278</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0167</v>
+        <v>0.0183</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>0</v>
@@ -3690,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0133</v>
+        <v>0.0161</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0318</v>
+        <v>0.0264</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,14 +3758,14 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>15</v>
@@ -3783,19 +3783,19 @@
         <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0264</v>
+        <v>0.0388</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -3897,7 +3897,7 @@
         <v>3.6</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0272</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-07T19:01:46.236347</t>
+          <t>2026-06-08T07:21:32.399683</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-08T08:46:31.720643</t>
+          <t>2026-06-08T11:52:50.581190</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>31.8</v>
+        <v>40.8</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>16.8</v>
+        <v>25.8</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>6</v>
@@ -834,10 +834,10 @@
         <v>4.8</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0456</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30.6</v>
+        <v>35.6</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>15.6</v>
+        <v>20.6</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -870,25 +870,25 @@
         <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>29.6</v>
+        <v>33</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14.6</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
@@ -930,16 +930,16 @@
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0179</v>
+        <v>0.0177</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29.6</v>
+        <v>32.4</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0207</v>
+        <v>0.0317</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>29</v>
+        <v>32.4</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>14</v>
+        <v>17.4</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0208</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>28.8</v>
+        <v>32.4</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>13.8</v>
+        <v>17.4</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1080,19 +1080,19 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0311</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>27.6</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12.6</v>
+        <v>17</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,25 +1125,25 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0244</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>26.4</v>
+        <v>31.8</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>11.4</v>
+        <v>16.8</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0173</v>
+        <v>0.0126</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>26.4</v>
+        <v>31.8</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>11.4</v>
+        <v>16.8</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -1236,16 +1236,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.0209</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>26</v>
+        <v>31.8</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>11</v>
+        <v>16.8</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1287,16 +1287,16 @@
         <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0301</v>
+        <v>0.0269</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>25.2</v>
+        <v>31.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.2</v>
+        <v>16.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0259</v>
+        <v>0.0189</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>23</v>
+        <v>31.4</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8</v>
+        <v>16.4</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,13 +1380,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0325</v>
+        <v>0.0141</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23</v>
+        <v>31.4</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8</v>
+        <v>16.4</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,25 +1431,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0275</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>23</v>
+        <v>31.4</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>8</v>
+        <v>16.4</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0343</v>
+        <v>0.0167</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,49 +1514,2446 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CS.PA</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>AI.PA</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>BNP.PA</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ML.PA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>1299.HK</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ACA.PA</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>1398.HK</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>2318.HK</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>EN.PA</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>ENGI.PA</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>AIR.PA</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>MC.PA</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>LR.PA</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>0016.HK</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>EL.PA</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>0388.HK</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>BN.PA</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>RMS.PA</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>9999.HK</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>0002.HK</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
           <t>ORA.PA</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B61" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="n">
+      <c r="C61" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
         <v>2.4</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5" t="n">
+      <c r="H61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M61" s="9" t="n">
         <v>0.0165</v>
       </c>
-      <c r="N16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>0027.HK</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="9" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -1677,7 +4074,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-08T11:52:50.581190</t>
+          <t>2026-06-08T14:10:02.978026</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>31.8</v>
+        <v>43.2</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>16.8</v>
+        <v>28.2</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>6</v>
@@ -837,7 +837,7 @@
         <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0215</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30.6</v>
+        <v>38.4</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -876,19 +876,19 @@
         <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.015</v>
+        <v>0.0186</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>29.6</v>
+        <v>35.6</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14.6</v>
+        <v>20.6</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0179</v>
+        <v>0.037</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29.6</v>
+        <v>35.4</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>14.6</v>
+        <v>20.4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0207</v>
+        <v>0.0322</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>29</v>
+        <v>34.2</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>14</v>
+        <v>19.2</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -1035,13 +1035,13 @@
         <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0277</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>28.8</v>
+        <v>33.6</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>13.8</v>
+        <v>18.6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1083,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0189</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>27.6</v>
+        <v>33.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>12.6</v>
+        <v>18.6</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1134,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0157</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>26.4</v>
+        <v>33</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>11.4</v>
+        <v>18</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0173</v>
+        <v>0.0147</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>26.4</v>
+        <v>32.4</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1233,19 +1233,19 @@
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.0319</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
         <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>5.6</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0301</v>
+        <v>0.0204</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>25.2</v>
+        <v>31.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.2</v>
+        <v>16.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1341,13 +1341,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0259</v>
+        <v>0.0189</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>23</v>
+        <v>31.4</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8</v>
+        <v>16.4</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,13 +1380,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0325</v>
+        <v>0.0142</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23</v>
+        <v>31.4</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8</v>
+        <v>16.4</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0169</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>23</v>
+        <v>30.8</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>8</v>
+        <v>15.8</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0343</v>
+        <v>0.0306</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>21</v>
+        <v>30.8</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>6</v>
+        <v>15.8</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1539,24 +1539,2319 @@
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>MRK</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>EL.PA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>3.6</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M21" s="9" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>BNP.PA</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2318.HK</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>0027.HK</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ML.PA</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>ORA.PA</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>0.0165</v>
       </c>
-      <c r="N16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="N31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>1299.HK</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>ACA.PA</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>1398.HK</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>AIR.PA</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>RMS.PA</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>LR.PA</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>0941.HK</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>0016.HK</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>AI.PA</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>9999.HK</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>0388.HK</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>0002.HK</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -1677,7 +3972,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-08T19:03:16.902216</t>
+          <t>2026-06-09T10:43:16.186202</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-09T14:04:57.310260</t>
+          <t>2026-06-09T17:15:05.308156</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>33</v>
+        <v>33.6</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -879,16 +879,16 @@
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0147</v>
+        <v>0.0157</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,25 +921,25 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0147</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>ML.PA</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -978,19 +978,19 @@
         <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0211</v>
+        <v>0.0213</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0211</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>30.8</v>
+        <v>31.4</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>15.8</v>
+        <v>16.4</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,13 +1074,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.0189</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,25 +1125,25 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0157</v>
+        <v>0.0306</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1506,6 +1506,57 @@
         <v>1</v>
       </c>
       <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>AI.PA</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -1626,7 +1677,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-09T17:15:05.308156</t>
+          <t>2026-06-09T17:53:30.049334</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>33.6</v>
+        <v>37.2</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>18.6</v>
+        <v>22.2</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -819,25 +819,25 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0283</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>33.6</v>
+        <v>36.8</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>18.6</v>
+        <v>21.8</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -870,25 +870,25 @@
         <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0157</v>
+        <v>0.0194</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>33</v>
+        <v>34.8</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>6</v>
@@ -936,10 +936,10 @@
         <v>2.4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0147</v>
+        <v>0.04</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>32</v>
+        <v>34.8</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0213</v>
+        <v>0.0318</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>31.8</v>
+        <v>34.4</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16.8</v>
+        <v>19.4</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0211</v>
+        <v>0.0193</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>31.4</v>
+        <v>34.4</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>16.4</v>
+        <v>19.4</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
@@ -1092,7 +1092,7 @@
         <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0189</v>
+        <v>0.0341</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30.8</v>
+        <v>33.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>15.8</v>
+        <v>18.6</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,25 +1125,25 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0306</v>
+        <v>0.0189</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>30</v>
+        <v>33.6</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>15</v>
+        <v>18.6</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1182,19 +1182,19 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0259</v>
+        <v>0.0157</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>29.6</v>
+        <v>33.6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14.6</v>
+        <v>18.6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -1239,13 +1239,13 @@
         <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0246</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>28.8</v>
+        <v>32.4</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>13.8</v>
+        <v>17.4</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1278,16 +1278,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>4.8</v>
@@ -1296,7 +1296,7 @@
         <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0165</v>
+        <v>0.0324</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>27.6</v>
+        <v>31.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>12.6</v>
+        <v>16.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1341,13 +1341,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M12" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0189</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>11</v>
+        <v>15.8</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1395,10 +1395,10 @@
         <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0346</v>
+        <v>0.0306</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>25.8</v>
+        <v>30.8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10.8</v>
+        <v>15.8</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,25 +1431,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0267</v>
+        <v>0.0139</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>23</v>
+        <v>30.8</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>8</v>
+        <v>15.8</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1488,19 +1488,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.0289</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,49 +1514,2395 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>CS.PA</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>EL.PA</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>BNP.PA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2318.HK</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>0027.HK</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ML.PA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>CA.PA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>ORA.PA</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>1299.HK</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>ACA.PA</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>1398.HK</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>AIR.PA</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>RMS.PA</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>AI.PA</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B46" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>LR.PA</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>0941.HK</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>0016.HK</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>9999.HK</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
         <v>22.8</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C58" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="D58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>0388.HK</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>0002.HK</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -1677,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-09T17:53:30.049334</t>
+          <t>2026-06-09T21:11:17.824446</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -828,16 +828,16 @@
         <v>0</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0142</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>33</v>
+        <v>34.4</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>18</v>
+        <v>19.4</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -876,19 +876,19 @@
         <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0147</v>
+        <v>0.0321</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0206</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31.8</v>
+        <v>30.6</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>16.8</v>
+        <v>15.6</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0</v>
@@ -981,16 +981,16 @@
         <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0211</v>
+        <v>0.0156</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>31.4</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0189</v>
+        <v>0.0211</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>30.8</v>
+        <v>29.6</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>15.8</v>
+        <v>14.6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0306</v>
+        <v>0.0197</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30.6</v>
+        <v>29.4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1140,10 +1140,10 @@
         <v>4.8</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0157</v>
+        <v>0.0205</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>30</v>
+        <v>28.8</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0259</v>
+        <v>0.0266</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>29.6</v>
+        <v>28.8</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,25 +1227,25 @@
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="K10" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0171</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>28.8</v>
+        <v>27.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0165</v>
+        <v>0.0196</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>27.6</v>
+        <v>25.2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>12.6</v>
+        <v>10.2</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M12" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0293</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1386,19 +1386,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0346</v>
+        <v>0.0263</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>25.8</v>
+        <v>20.4</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,25 +1431,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0267</v>
+        <v>0.0196</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>RMS.PA</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>23</v>
+        <v>20.4</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1488,19 +1488,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.033</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-09T21:22:22.510100</t>
+          <t>2026-06-10T12:53:42.185106</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>34.4</v>
+        <v>38.4</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>19.4</v>
+        <v>23.4</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -825,19 +825,19 @@
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0281</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>34.4</v>
+        <v>35.6</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0</v>
@@ -879,16 +879,16 @@
         <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0321</v>
+        <v>0.0455</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>32</v>
+        <v>35.6</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>17</v>
+        <v>20.6</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,25 +921,25 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0249</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>30.6</v>
+        <v>35.4</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>15.6</v>
+        <v>20.4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>3</v>
@@ -987,10 +987,10 @@
         <v>4.8</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0447</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>30</v>
+        <v>35.4</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>20.4</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0211</v>
+        <v>0.0241</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>29.6</v>
+        <v>34.4</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>14.6</v>
+        <v>19.4</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,13 +1074,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>6</v>
@@ -1089,10 +1089,10 @@
         <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.0142</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29.4</v>
+        <v>34.4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>14.4</v>
+        <v>19.4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1131,19 +1131,19 @@
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L8" s="5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M8" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0321</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>28.8</v>
+        <v>34.4</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>13.8</v>
+        <v>19.4</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0266</v>
+        <v>0.026</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>28.8</v>
+        <v>34.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13.8</v>
+        <v>19.2</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,13 +1227,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>3</v>
@@ -1245,7 +1245,7 @@
         <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0171</v>
+        <v>0.0352</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>27.6</v>
+        <v>32.4</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>12.6</v>
+        <v>17.4</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1284,19 +1284,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0414</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>25.2</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.2</v>
+        <v>17</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1338,16 +1338,16 @@
         <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.0257</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>21</v>
+        <v>30.8</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>6</v>
+        <v>15.8</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1386,19 +1386,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.0139</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>20.4</v>
+        <v>30.8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5.4</v>
+        <v>15.8</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1443,13 +1443,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.025</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>20.4</v>
+        <v>30.8</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>5.4</v>
+        <v>15.8</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1491,21 +1491,2418 @@
         <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>TMO</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>ENGI.PA</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>CA.PA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>BNP.PA</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2318.HK</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ACA.PA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ML.PA</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>EL.PA</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ORA.PA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>AI.PA</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>9999.HK</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>0941.HK</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>1299.HK</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>MC.PA</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>EN.PA</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>0388.HK</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>0002.HK</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>0027.HK</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>DHR</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>0016.HK</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>1398.HK</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>LR.PA</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>BN.PA</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>RMS.PA</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
         <v>0.033</v>
       </c>
-      <c r="N15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -1626,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-10T12:53:42.185106</t>
+          <t>2026-06-10T13:09:33.771424</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -837,7 +837,7 @@
         <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0281</v>
+        <v>0.0249</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,7 +851,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
@@ -870,25 +870,25 @@
         <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0455</v>
+        <v>0.0249</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>35.6</v>
+        <v>34.8</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,25 +921,25 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0249</v>
+        <v>0.0398</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20.4</v>
+        <v>19.4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -984,13 +984,13 @@
         <v>3</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0447</v>
+        <v>0.0195</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>35.4</v>
+        <v>34.4</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20.4</v>
+        <v>19.4</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1032,16 +1032,16 @@
         <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M6" s="6" t="n">
-        <v>0.0241</v>
+        <v>0.0321</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -1074,13 +1074,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>6</v>
@@ -1089,10 +1089,10 @@
         <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0142</v>
+        <v>0.0341</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>5.6</v>
@@ -1143,7 +1143,7 @@
         <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.0308</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>34.4</v>
+        <v>33.6</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>19.4</v>
+        <v>18.6</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>0</v>
@@ -1185,16 +1185,16 @@
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.026</v>
+        <v>0.0265</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>34.2</v>
+        <v>32.4</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,13 +1227,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>3</v>
@@ -1245,7 +1245,7 @@
         <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0352</v>
+        <v>0.032</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1296,7 +1296,7 @@
         <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0414</v>
+        <v>0.0342</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0257</v>
+        <v>0.0197</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>30.8</v>
+        <v>31.4</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>15.8</v>
+        <v>16.4</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,25 +1380,25 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0139</v>
+        <v>0.0142</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>30.8</v>
+        <v>31.4</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>15.8</v>
+        <v>16.4</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0218</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>30.8</v>
+        <v>31.4</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>15.8</v>
+        <v>16.4</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0378</v>
+        <v>0.0279</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1542,16 +1542,16 @@
         <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0203</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,25 +1584,25 @@
         <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="8" t="n">
         <v>2.4</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L17" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0387</v>
+        <v>0.0269</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1653,7 +1653,7 @@
         <v>4.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0253</v>
+        <v>0.0142</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,25 +1686,25 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M19" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0235</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1737,25 +1737,25 @@
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0176</v>
+        <v>0.0297</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1794,19 +1794,19 @@
         <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K21" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M21" s="9" t="n">
-        <v>0.0211</v>
+        <v>0.0236</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1848,16 +1848,16 @@
         <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.0216</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1890,25 +1890,25 @@
         <v>0</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="K23" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.0246</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1941,25 +1941,25 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="6" t="n">
-        <v>0.0461</v>
+        <v>0.0176</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>29.6</v>
+        <v>30</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0235</v>
+        <v>0.0211</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,7 +2024,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2094,25 +2094,25 @@
         <v>0</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0243</v>
+        <v>0.02</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,7 +2126,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
@@ -2160,10 +2160,10 @@
         <v>4.8</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0243</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,7 +2177,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -2214,7 +2214,7 @@
         <v>3.6</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0255</v>
+        <v>0.0205</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2400,25 +2400,25 @@
         <v>0</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.025</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -2451,25 +2451,25 @@
         <v>0</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L34" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M34" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.0246</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,7 +2483,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -2511,16 +2511,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0235</v>
+        <v>0.0223</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2553,25 +2553,25 @@
         <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L36" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0299</v>
+        <v>0.0221</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0373</v>
+        <v>0.0156</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -2706,25 +2706,25 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0328</v>
+        <v>0.0308</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2757,25 +2757,25 @@
         <v>0</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0257</v>
+        <v>0.0197</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,7 +2789,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0381</v>
+        <v>0.0176</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,7 +2840,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0186</v>
+        <v>0.0381</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2910,25 +2910,25 @@
         <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0309</v>
+        <v>0.0186</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2993,7 +2993,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>0</v>
@@ -3027,10 +3027,10 @@
         <v>4.8</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0414</v>
+        <v>0.0207</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3234,7 +3234,7 @@
         <v>1.8</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0347</v>
+        <v>0.0283</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0196</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,7 +3299,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -3336,7 +3336,7 @@
         <v>3.6</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0342</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3503,14 +3503,14 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>15</v>
@@ -3522,25 +3522,25 @@
         <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0371</v>
+        <v>0.0317</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,14 +3554,14 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>15</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>0</v>
@@ -3585,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0317</v>
+        <v>0.0206</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,14 +3605,14 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>15</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0263</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,14 +3656,14 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>15</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J58" s="5" t="n">
         <v>0</v>
@@ -3690,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0263</v>
+        <v>0.0196</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>RMS.PA</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -3732,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0253</v>
+        <v>0.033</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0199</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,7 +3809,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.033</v>
+        <v>0.0226</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0296</v>
+        <v>0.0276</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-10T13:09:33.771424</t>
+          <t>2026-06-10T18:16:32.146641</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>38.4</v>
+        <v>36.8</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>23.4</v>
+        <v>21.8</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
@@ -831,13 +831,13 @@
         <v>6</v>
       </c>
       <c r="K2" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L2" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L2" s="5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M2" s="6" t="n">
-        <v>0.0249</v>
+        <v>0.0198</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>34.8</v>
+        <v>34.4</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
@@ -930,16 +930,16 @@
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0398</v>
+        <v>0.0321</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0143</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1023,16 +1023,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>5.6</v>
@@ -1041,7 +1041,7 @@
         <v>4.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.0342</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
@@ -1092,7 +1092,7 @@
         <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0341</v>
+        <v>0.031</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -1134,16 +1134,16 @@
         <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0308</v>
+        <v>0.0252</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1194,7 +1194,7 @@
         <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0265</v>
+        <v>0.0271</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.032</v>
+        <v>0.0323</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,7 +1259,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1278,25 +1278,25 @@
         <v>0</v>
       </c>
       <c r="G11" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0342</v>
+        <v>0.0401</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0142</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,7 +1361,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -1386,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
         <v>5.6</v>
@@ -1398,7 +1398,7 @@
         <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0142</v>
+        <v>0.022</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1431,25 +1431,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.0203</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
@@ -1491,16 +1491,16 @@
         <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0279</v>
+        <v>0.0245</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,7 +1514,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1533,25 +1533,25 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0203</v>
+        <v>0.0205</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1653,7 +1653,7 @@
         <v>4.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0236</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,7 +1667,7 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -1695,16 +1695,16 @@
         <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0235</v>
+        <v>0.0295</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -1746,16 +1746,16 @@
         <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0297</v>
+        <v>0.0287</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1788,25 +1788,25 @@
         <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0236</v>
+        <v>0.0156</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,7 +1820,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -1857,7 +1857,7 @@
         <v>4.8</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0224</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,7 +1871,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -1908,7 +1908,7 @@
         <v>6</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0246</v>
+        <v>0.0176</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -1950,16 +1950,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0176</v>
+        <v>0.0211</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0211</v>
+        <v>0.0246</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,7 +2024,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0245</v>
+        <v>0.0201</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2094,25 +2094,25 @@
         <v>0</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.02</v>
+        <v>0.0243</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,7 +2126,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
@@ -2160,10 +2160,10 @@
         <v>4.8</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0243</v>
+        <v>0.0205</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>ML.PA</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2196,25 +2196,25 @@
         <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.0206</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>EL.PA</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>3</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0266</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,7 +2279,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -2298,25 +2298,25 @@
         <v>0</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0266</v>
+        <v>0.0171</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2349,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0171</v>
+        <v>0.0249</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2400,25 +2400,25 @@
         <v>0</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.025</v>
+        <v>0.0222</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2457,19 +2457,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0246</v>
+        <v>0.0356</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>28.2</v>
+        <v>27</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2502,25 +2502,25 @@
         <v>0</v>
       </c>
       <c r="G35" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0223</v>
+        <v>0.0311</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>28.2</v>
+        <v>26.6</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2553,25 +2553,25 @@
         <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0221</v>
+        <v>0.0197</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>27.6</v>
+        <v>26.6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2613,16 +2613,16 @@
         <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0264</v>
+        <v>0.0176</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>27.6</v>
+        <v>26.6</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>12.6</v>
+        <v>11.6</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2667,13 +2667,13 @@
         <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0381</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>0</v>
@@ -2715,16 +2715,16 @@
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0308</v>
+        <v>0.0186</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>3</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>5.6</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0381</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2820,13 +2820,13 @@
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0176</v>
+        <v>0.0216</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2871,13 +2871,13 @@
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.0208</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2910,25 +2910,25 @@
         <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" s="9" t="n">
-        <v>0.0186</v>
+        <v>0.015</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2961,25 +2961,25 @@
         <v>0</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.0365</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3012,25 +3012,25 @@
         <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L45" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" s="9" t="n">
-        <v>0.0207</v>
+        <v>0.0293</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>0</v>
@@ -3072,16 +3072,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.015</v>
+        <v>0.0284</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>0</v>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0365</v>
+        <v>0.0247</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3165,13 +3165,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
         <v>0</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.0196</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
@@ -3225,16 +3225,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0283</v>
+        <v>0.0348</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0248</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I51" s="8" t="n">
         <v>0</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0342</v>
+        <v>0.0197</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,7 +3350,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -3372,22 +3372,22 @@
         <v>2.4</v>
       </c>
       <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
         <v>4.8</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.017</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -3438,7 +3438,7 @@
         <v>1.8</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.017</v>
+        <v>0.0277</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3477,19 +3477,19 @@
         <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0277</v>
+        <v>0.0226</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3809,14 +3809,14 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>15</v>
@@ -3834,75 +3834,24 @@
         <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0226</v>
+        <v>0.0277</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
       </c>
       <c r="O61" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="6" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -4023,7 +3972,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-10T18:16:32.146641</t>
+          <t>2026-06-10T19:51:03.650461</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -837,7 +837,7 @@
         <v>4.8</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0198</v>
+        <v>0.0199</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
         <v>4.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0342</v>
+        <v>0.0343</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.031</v>
+        <v>0.0311</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>33.6</v>
+        <v>32.4</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>18.6</v>
+        <v>17.4</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1191,10 +1191,10 @@
         <v>2.4</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0271</v>
+        <v>0.0402</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>32.4</v>
+        <v>31.4</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1239,13 +1239,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0323</v>
+        <v>0.0142</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>32.4</v>
+        <v>31.4</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17.4</v>
+        <v>16.4</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0401</v>
+        <v>0.022</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0202</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1392,13 +1392,13 @@
         <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.022</v>
+        <v>0.0245</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1440,16 +1440,16 @@
         <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,7 +1463,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1488,19 +1488,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0245</v>
+        <v>0.0271</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
@@ -1542,16 +1542,16 @@
         <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0237</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,25 +1584,25 @@
         <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0269</v>
+        <v>0.0295</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1653,7 +1653,7 @@
         <v>4.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0236</v>
+        <v>0.0287</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,25 +1686,25 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0295</v>
+        <v>0.0156</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1737,25 +1737,25 @@
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0287</v>
+        <v>0.0249</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1788,25 +1788,25 @@
         <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M21" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0272</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,7 +1820,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>4.8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0224</v>
+        <v>0.0176</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
@@ -1899,16 +1899,16 @@
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0176</v>
+        <v>0.0211</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1941,25 +1941,25 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0211</v>
+        <v>0.0197</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0246</v>
+        <v>0.0245</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         <v>1.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0249</v>
+        <v>0.025</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,7 +2381,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -2409,16 +2409,16 @@
         <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.0224</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2457,19 +2457,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.0222</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AI.PA</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>3.6</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.0264</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0</v>
@@ -2562,16 +2562,16 @@
         <v>3</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0356</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>0</v>
@@ -2613,16 +2613,16 @@
         <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0176</v>
+        <v>0.0311</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,7 +2636,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.0177</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0186</v>
+        <v>0.0381</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2757,13 +2757,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.0186</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2808,25 +2808,25 @@
         <v>0</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0216</v>
+        <v>0.0381</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,7 +2840,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0208</v>
+        <v>0.0215</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,7 +2891,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -2910,25 +2910,25 @@
         <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="H43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.015</v>
+        <v>0.0207</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,7 +2942,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -2979,7 +2979,7 @@
         <v>6</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0365</v>
+        <v>0.015</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3012,13 +3012,13 @@
         <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>0</v>
@@ -3027,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0293</v>
+        <v>0.0365</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,7 +3044,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -3069,19 +3069,19 @@
         <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.0293</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,7 +3095,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0247</v>
+        <v>0.0284</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>24.6</v>
+        <v>25.2</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0248</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,7 +3197,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -3234,7 +3234,7 @@
         <v>3.6</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0348</v>
+        <v>0.0196</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0248</v>
+        <v>0.0324</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
         <v>0</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.0349</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,7 +3350,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -3372,7 +3372,7 @@
         <v>2.4</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>0</v>
@@ -3381,13 +3381,13 @@
         <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.017</v>
+        <v>0.0197</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,7 +3401,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -3438,7 +3438,7 @@
         <v>1.8</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.0277</v>
+        <v>0.017</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3477,19 +3477,19 @@
         <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0226</v>
+        <v>0.0277</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,7 +3503,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -3522,25 +3522,25 @@
         <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0317</v>
+        <v>0.0226</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,14 +3554,14 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>15</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>0</v>
@@ -3585,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0317</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,14 +3605,14 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>15</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.0206</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,14 +3656,14 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>15</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" s="5" t="n">
         <v>0</v>
@@ -3690,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0263</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,7 +3707,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.033</v>
+        <v>0.0196</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>RMS.PA</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0199</v>
+        <v>0.033</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,14 +3809,14 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>15</v>
@@ -3834,24 +3834,75 @@
         <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="L61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="N61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -3972,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-10T19:51:03.650461</t>
+          <t>2026-06-10T21:41:40.574328</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-10T21:41:40.574328</t>
+          <t>2026-06-10T21:52:24.993717</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>36.8</v>
+        <v>38.4</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>21.8</v>
+        <v>23.4</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
@@ -831,13 +831,13 @@
         <v>6</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0199</v>
+        <v>0.0388</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>35.6</v>
+        <v>36.8</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -870,25 +870,25 @@
         <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0249</v>
+        <v>0.0198</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>34.4</v>
+        <v>36.8</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>19.4</v>
+        <v>21.8</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>5.6</v>
@@ -939,7 +939,7 @@
         <v>4.8</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.02</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0143</v>
+        <v>0.0201</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>EL.PA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>5.6</v>
@@ -1041,7 +1041,7 @@
         <v>4.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0343</v>
+        <v>0.0272</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>33.8</v>
+        <v>34.4</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
@@ -1092,7 +1092,7 @@
         <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.0343</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,25 +1125,25 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>6</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0252</v>
+        <v>0.0142</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>32.4</v>
+        <v>33.6</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>17.4</v>
+        <v>18.6</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>0</v>
@@ -1188,13 +1188,13 @@
         <v>6</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0402</v>
+        <v>0.0251</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>31.4</v>
+        <v>32.6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>16.4</v>
+        <v>17.6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,13 +1227,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>3</v>
@@ -1242,10 +1242,10 @@
         <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0239</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>31.4</v>
+        <v>32.4</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1284,19 +1284,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.022</v>
+        <v>0.0223</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
@@ -1338,16 +1338,16 @@
         <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0202</v>
+        <v>0.0247</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>RMS.PA</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1386,19 +1386,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0245</v>
+        <v>0.0349</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>3</v>
@@ -1446,10 +1446,10 @@
         <v>2.4</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0204</v>
+        <v>0.0161</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,7 +1463,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1488,19 +1488,19 @@
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0271</v>
+        <v>0.0141</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1533,25 +1533,25 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0237</v>
+        <v>0.0365</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>3</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0295</v>
+        <v>0.0267</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1653,7 +1653,7 @@
         <v>4.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0287</v>
+        <v>0.0296</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,25 +1686,25 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M19" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0229</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1737,25 +1737,25 @@
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0249</v>
+        <v>0.028</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1797,16 +1797,16 @@
         <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0272</v>
+        <v>0.0242</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,7 +1820,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -1839,25 +1839,25 @@
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="M22" s="6" t="n">
-        <v>0.0176</v>
+        <v>0.02</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
@@ -1899,16 +1899,16 @@
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0211</v>
+        <v>0.0197</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -1950,16 +1950,16 @@
         <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0316</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1992,25 +1992,25 @@
         <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="K25" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="9" t="n">
-        <v>0.0245</v>
+        <v>0.0177</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,7 +2024,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0201</v>
+        <v>0.0247</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2094,25 +2094,25 @@
         <v>0</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0243</v>
+        <v>0.0202</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0</v>
@@ -2157,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0208</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>29</v>
+        <v>29.4</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2196,25 +2196,25 @@
         <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0251</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>28.8</v>
+        <v>29.4</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2247,25 +2247,25 @@
         <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.03</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>28.8</v>
+        <v>29.4</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2298,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="8" t="n">
         <v>4.8</v>
@@ -2316,7 +2316,7 @@
         <v>3.6</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0171</v>
+        <v>0.0338</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,7 +2330,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -2349,16 +2349,16 @@
         <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>5.6</v>
@@ -2367,7 +2367,7 @@
         <v>1.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,7 +2381,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -2418,7 +2418,7 @@
         <v>4.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0224</v>
+        <v>0.0232</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -2469,7 +2469,7 @@
         <v>1.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0172</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2502,25 +2502,25 @@
         <v>0</v>
       </c>
       <c r="G35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="K35" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0264</v>
+        <v>0.0267</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.0214</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2610,19 +2610,19 @@
         <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.0287</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AI.PA</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0177</v>
+        <v>0.0263</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2706,25 +2706,25 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0381</v>
+        <v>0.0212</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2769,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0186</v>
+        <v>0.0218</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2808,25 +2808,25 @@
         <v>0</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0381</v>
+        <v>0.0267</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>25.8</v>
+        <v>27</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>0</v>
@@ -2874,10 +2874,10 @@
         <v>4.8</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.02</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2910,25 +2910,25 @@
         <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0207</v>
+        <v>0.0216</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,7 +2942,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -2961,25 +2961,25 @@
         <v>0</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="H44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="5" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.015</v>
+        <v>0.0205</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,7 +2993,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -3030,7 +3030,7 @@
         <v>6</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0365</v>
+        <v>0.0151</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3069,19 +3069,19 @@
         <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.0166</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3132,7 +3132,7 @@
         <v>1.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0284</v>
+        <v>0.0294</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0248</v>
+        <v>0.0331</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,7 +3197,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -3234,7 +3234,7 @@
         <v>3.6</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0355</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.0232</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>24.6</v>
+        <v>23.6</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,25 +3318,25 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0349</v>
+        <v>0.0342</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,14 +3350,14 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>15</v>
@@ -3372,22 +3372,22 @@
         <v>2.4</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.0193</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,14 +3401,14 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>15</v>
@@ -3420,25 +3420,25 @@
         <v>0</v>
       </c>
       <c r="G53" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
         <v>2.4</v>
       </c>
-      <c r="H53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L53" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.017</v>
+        <v>0.0229</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3471,25 +3471,25 @@
         <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L54" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0277</v>
+        <v>0.0205</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,7 +3503,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -3522,25 +3522,25 @@
         <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
         <v>2.4</v>
       </c>
-      <c r="H55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K55" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0226</v>
+        <v>0.0192</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3591,7 +3591,7 @@
         <v>3.6</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0317</v>
+        <v>0.0322</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0312</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,14 +3656,14 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>15</v>
@@ -3687,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0263</v>
+        <v>0.0387</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>20.4</v>
+        <v>23</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -3732,19 +3732,19 @@
         <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0205</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,14 +3758,14 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>15</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" s="5" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.033</v>
+        <v>0.0277</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,7 +3809,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0199</v>
+        <v>0.0196</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
@@ -3860,14 +3860,14 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>ML.PA</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>15</v>
@@ -3888,16 +3888,16 @@
         <v>0</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0278</v>
+        <v>0.0204</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-10T21:52:24.993717</t>
+          <t>2026-06-11T15:10:10.069581</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,7 +800,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -837,7 +837,7 @@
         <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0388</v>
+        <v>0.0254</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -888,7 +888,7 @@
         <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0198</v>
+        <v>0.0201</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>4.8</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0201</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>34.4</v>
+        <v>36</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>19.4</v>
+        <v>21</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0201</v>
+        <v>0.0399</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>34.4</v>
+        <v>34.8</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1035,13 +1035,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0272</v>
+        <v>0.0349</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0343</v>
+        <v>0.02</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>EL.PA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33.8</v>
+        <v>34.4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1125,16 +1125,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>5.6</v>
@@ -1143,7 +1143,7 @@
         <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0272</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1185,16 +1185,16 @@
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.0141</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>32.6</v>
+        <v>34.4</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1236,16 +1236,16 @@
         <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0239</v>
+        <v>0.0344</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>32.4</v>
+        <v>34.4</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1284,19 +1284,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0223</v>
+        <v>0.0174</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>32.4</v>
+        <v>33.8</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0247</v>
+        <v>0.0142</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>31.4</v>
+        <v>33.8</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>16.4</v>
+        <v>18.8</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,16 +1380,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="8" t="n">
         <v>5.6</v>
@@ -1398,7 +1398,7 @@
         <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0349</v>
+        <v>0.0194</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1443,13 +1443,13 @@
         <v>3</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0161</v>
+        <v>0.0224</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>31.2</v>
+        <v>32.4</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0141</v>
+        <v>0.0247</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>RMS.PA</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1533,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0365</v>
+        <v>0.0349</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>0</v>
@@ -1593,16 +1593,16 @@
         <v>3</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0277</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1635,25 +1635,25 @@
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L18" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0296</v>
+        <v>0.0161</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,25 +1686,25 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0229</v>
+        <v>0.0365</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
@@ -1749,13 +1749,13 @@
         <v>3</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1806,7 +1806,7 @@
         <v>4.8</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0242</v>
+        <v>0.0296</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1848,16 +1848,16 @@
         <v>3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0228</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1890,25 +1890,25 @@
         <v>0</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.0285</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>BNP.PA</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -1959,7 +1959,7 @@
         <v>4.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0316</v>
+        <v>0.02</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,7 +1973,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>4.8</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0197</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
@@ -2052,16 +2052,16 @@
         <v>3</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0247</v>
+        <v>0.0327</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2094,25 +2094,25 @@
         <v>0</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="K27" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="9" t="n">
-        <v>0.0202</v>
+        <v>0.0177</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,7 +2126,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -2145,25 +2145,25 @@
         <v>0</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0208</v>
+        <v>0.0248</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2196,25 +2196,25 @@
         <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.0206</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2250,22 +2250,22 @@
         <v>4.8</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03</v>
+        <v>0.0208</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,7 +2279,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -2298,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>0</v>
@@ -2313,10 +2313,10 @@
         <v>4.8</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0338</v>
+        <v>0.0251</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>28.4</v>
+        <v>29.4</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2349,25 +2349,25 @@
         <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2400,25 +2400,25 @@
         <v>0</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0232</v>
+        <v>0.0239</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0172</v>
+        <v>0.0218</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,7 +2483,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -2502,16 +2502,16 @@
         <v>0</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>6</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>2.4</v>
@@ -2520,7 +2520,7 @@
         <v>1.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0172</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2571,7 +2571,7 @@
         <v>1.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0214</v>
+        <v>0.0216</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2622,7 +2622,7 @@
         <v>1.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0287</v>
+        <v>0.0293</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,7 +2636,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>AI.PA</t>
+          <t>CA.PA</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -2655,25 +2655,25 @@
         <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0263</v>
+        <v>0.0212</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,7 +2687,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>0</v>
@@ -2715,16 +2715,16 @@
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0212</v>
+        <v>0.0249</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,7 +2738,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -2775,7 +2775,7 @@
         <v>1.8</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.0267</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>27.6</v>
+        <v>27</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
@@ -2823,10 +2823,10 @@
         <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0267</v>
+        <v>0.0202</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2868,16 +2868,16 @@
         <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0312</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0216</v>
+        <v>0.0218</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -3095,7 +3095,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -3120,19 +3120,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0294</v>
+        <v>0.0247</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>24.6</v>
+        <v>25.2</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3165,25 +3165,25 @@
         <v>0</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0331</v>
+        <v>0.029</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,7 +3197,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -3234,7 +3234,7 @@
         <v>3.6</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0355</v>
+        <v>0.0337</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0232</v>
+        <v>0.0351</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,25 +3318,25 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0342</v>
+        <v>0.0234</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,14 +3350,14 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>15</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>0</v>
@@ -3378,16 +3378,16 @@
         <v>3</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0193</v>
+        <v>0.0342</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.0229</v>
+        <v>0.023</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0312</v>
+        <v>0.0387</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0387</v>
+        <v>0.0205</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -3738,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.0277</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,14 +3758,14 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>15</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J60" s="5" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0277</v>
+        <v>0.0196</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,7 +3809,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>ML.PA</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
@@ -3834,11 +3834,11 @@
         <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J61" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="K61" s="8" t="n">
         <v>0</v>
       </c>
@@ -3846,63 +3846,12 @@
         <v>0</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0204</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
       </c>
       <c r="O61" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>ML.PA</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="C62" s="5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="6" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -4023,7 +3972,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-11T15:10:10.069581</t>
+          <t>2026-06-11T18:41:36.411187</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>38.4</v>
+        <v>44.4</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>23.4</v>
+        <v>29.4</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>6</v>
@@ -828,16 +828,16 @@
         <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0396</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>36.8</v>
+        <v>41.3</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>21.8</v>
+        <v>26.3</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -867,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>0</v>
@@ -879,16 +879,16 @@
         <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0201</v>
+        <v>0.0254</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>36.8</v>
+        <v>40.7</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>21.8</v>
+        <v>25.7</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -918,28 +918,28 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="M4" s="6" t="n">
-        <v>0.0201</v>
+        <v>0.0413</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>36</v>
+        <v>40.5</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>21</v>
+        <v>25.5</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>6</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0399</v>
+        <v>0.02</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>34.8</v>
+        <v>39.9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>19.8</v>
+        <v>24.9</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1020,10 +1020,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -1032,16 +1032,16 @@
         <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.0201</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>34.4</v>
+        <v>39.6</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>19.4</v>
+        <v>24.6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.02</v>
+        <v>0.0343</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>EL.PA</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>34.4</v>
+        <v>39.5</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>19.4</v>
+        <v>24.5</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>6</v>
@@ -1134,16 +1134,16 @@
         <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0272</v>
+        <v>0.05</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>34.4</v>
+        <v>39.5</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>19.4</v>
+        <v>24.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>6</v>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0141</v>
+        <v>0.035</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>34.4</v>
+        <v>39.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>19.4</v>
+        <v>24.2</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -1236,16 +1236,16 @@
         <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0344</v>
+        <v>0.0247</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>34.4</v>
+        <v>37.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>19.4</v>
+        <v>22.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>5.6</v>
@@ -1296,7 +1296,7 @@
         <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0174</v>
+        <v>0.0143</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>33.8</v>
+        <v>37.3</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>18.8</v>
+        <v>22.3</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2.4</v>
@@ -1335,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>5.6</v>
@@ -1347,7 +1347,7 @@
         <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0201</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>33.8</v>
+        <v>37.3</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>18.8</v>
+        <v>22.3</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
@@ -1389,16 +1389,16 @@
         <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0194</v>
+        <v>0.027</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>32.4</v>
+        <v>36.9</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>17.4</v>
+        <v>21.9</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,28 +1428,28 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0224</v>
+        <v>0.0286</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>32.4</v>
+        <v>36.7</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>17.4</v>
+        <v>21.7</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>6</v>
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0247</v>
+        <v>0.0174</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RMS.PA</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>31.4</v>
+        <v>36.7</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,13 +1530,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.0365</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>31.4</v>
+        <v>36.7</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,28 +1581,28 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0277</v>
+        <v>0.0205</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>31.2</v>
+        <v>36.6</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1632,28 +1632,28 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0161</v>
+        <v>0.0279</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>31.2</v>
+        <v>35.2</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>16.2</v>
+        <v>20.2</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1683,28 +1683,28 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0365</v>
+        <v>0.0325</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>31.2</v>
+        <v>35.2</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>16.2</v>
+        <v>20.2</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.027</v>
+        <v>0.0342</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>30.8</v>
+        <v>34.8</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>15.8</v>
+        <v>19.8</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>0</v>
@@ -1797,16 +1797,16 @@
         <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0296</v>
+        <v>0.0248</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>30.8</v>
+        <v>34.6</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>15.8</v>
+        <v>19.6</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,28 +1836,28 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K22" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L22" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0228</v>
+        <v>0.0192</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>30.8</v>
+        <v>33.8</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0285</v>
+        <v>0.0224</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>30.6</v>
+        <v>33.1</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>15.6</v>
+        <v>18.1</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>2.4</v>
@@ -1950,16 +1950,16 @@
         <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0227</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>30.6</v>
+        <v>32.9</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>15.6</v>
+        <v>17.9</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K25" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.0287</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,28 +2040,28 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0327</v>
+        <v>0.0151</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>30.6</v>
+        <v>32.5</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0205</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>29.6</v>
+        <v>32.2</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>14.6</v>
+        <v>17.2</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
@@ -2154,16 +2154,16 @@
         <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0248</v>
+        <v>0.024</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>14.6</v>
+        <v>15.6</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2196,25 +2196,25 @@
         <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L29" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="K29" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0177</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>29.6</v>
+        <v>30.5</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0208</v>
+        <v>0.0322</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>29.4</v>
+        <v>30.5</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>14.4</v>
+        <v>15.5</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>0</v>
@@ -2313,10 +2313,10 @@
         <v>4.8</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.0166</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>29.4</v>
+        <v>30.1</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,28 +2346,28 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.03</v>
+        <v>0.0216</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>28.4</v>
+        <v>30.1</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>13.4</v>
+        <v>15.1</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>3</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>5.6</v>
@@ -2418,7 +2418,7 @@
         <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0239</v>
+        <v>0.0293</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>28.2</v>
+        <v>29.9</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>6</v>
@@ -2463,13 +2463,13 @@
         <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.025</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>28.2</v>
+        <v>29.9</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2499,10 +2499,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0172</v>
+        <v>0.03</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>27.8</v>
+        <v>29.9</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>12.8</v>
+        <v>14.9</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>2.4</v>
@@ -2565,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0248</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>27.8</v>
+        <v>29.6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>12.8</v>
+        <v>14.6</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2604,25 +2604,25 @@
         <v>0</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0293</v>
+        <v>0.0208</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>27.6</v>
+        <v>29.4</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0212</v>
+        <v>0.0251</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>27.6</v>
+        <v>29.4</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2721,10 +2721,10 @@
         <v>4.8</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0249</v>
+        <v>0.0445</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>27.6</v>
+        <v>29.3</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>4.8</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0267</v>
+        <v>0.0202</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>27</v>
+        <v>28.3</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>12</v>
+        <v>13.3</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2.4</v>
@@ -2814,19 +2814,19 @@
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0202</v>
+        <v>0.0217</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>26</v>
+        <v>28.1</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2856,28 +2856,28 @@
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.034</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>26</v>
+        <v>27.6</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2910,22 +2910,22 @@
         <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" s="9" t="n">
         <v>0.0218</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>25.8</v>
+        <v>27.6</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>10.8</v>
+        <v>12.6</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>0</v>
@@ -2976,10 +2976,10 @@
         <v>4.8</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0267</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0151</v>
+        <v>0.0193</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>25.8</v>
+        <v>26.9</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3060,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>0</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0166</v>
+        <v>0.0337</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>2.4</v>
@@ -3120,19 +3120,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0247</v>
+        <v>0.0233</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3162,28 +3162,28 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.029</v>
+        <v>0.0229</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>6</v>
@@ -3228,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0337</v>
+        <v>0.0205</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3264,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0351</v>
+        <v>0.0387</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
@@ -3330,528 +3330,18 @@
         <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0234</v>
+        <v>0.0349</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
       </c>
       <c r="O51" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>9999.HK</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="6" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="C53" s="8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="9" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="N53" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="6" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>0939.HK</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="C55" s="8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D55" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="9" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="N55" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>0016.HK</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M56" s="6" t="n">
-        <v>0.0322</v>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>0700.HK</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C57" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="9" t="n">
-        <v>0.0387</v>
-      </c>
-      <c r="N57" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>1398.HK</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="6" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>LR.PA</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C59" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D59" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M59" s="9" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="N59" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="8" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>BN.PA</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="6" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>ML.PA</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="C61" s="8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="n">
-        <v>0.0204</v>
-      </c>
-      <c r="N61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -3972,7 +3462,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-11T18:41:36.411187</t>
+          <t>2026-06-11T19:30:29.421080</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>44.4</v>
+        <v>43.7</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>29.4</v>
+        <v>28.7</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>6</v>
@@ -831,13 +831,13 @@
         <v>4.2</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0396</v>
+        <v>0.0254</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>41.3</v>
+        <v>43.5</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>26.3</v>
+        <v>28.5</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>6</v>
@@ -879,16 +879,16 @@
         <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.0209</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>40.7</v>
+        <v>41.9</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>25.7</v>
+        <v>26.9</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -924,22 +924,22 @@
         <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0413</v>
+        <v>0.0353</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>25.5</v>
+        <v>26.2</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -981,16 +981,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.02</v>
+        <v>0.0398</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>24.9</v>
+        <v>25.5</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,7 +1023,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -1038,10 +1038,10 @@
         <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0201</v>
+        <v>0.02</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0343</v>
+        <v>0.0345</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1143,7 +1143,7 @@
         <v>1.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.05</v>
+        <v>0.0502</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1185,16 +1185,16 @@
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.035</v>
+        <v>0.0247</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>39.2</v>
+        <v>37.6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,7 +1227,7 @@
         <v>4.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -1239,13 +1239,13 @@
         <v>2.1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0247</v>
+        <v>0.0143</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,7 +1259,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1296,7 +1296,7 @@
         <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0143</v>
+        <v>0.0195</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>37.3</v>
+        <v>36.9</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1380,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         <v>2.1</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.027</v>
+        <v>0.0289</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1440,16 +1440,16 @@
         <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.0175</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,7 +1463,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1482,25 +1482,25 @@
         <v>2.3</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0174</v>
+        <v>0.0365</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,7 +1514,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1530,28 +1530,28 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0365</v>
+        <v>0.0205</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,16 +1581,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>4.2</v>
@@ -1599,10 +1599,10 @@
         <v>5.6</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.028</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1632,28 +1632,28 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0279</v>
+        <v>0.0416</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>35.2</v>
+        <v>36.4</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1683,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2.4</v>
@@ -1701,10 +1701,10 @@
         <v>5.6</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0325</v>
+        <v>0.0242</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -1734,13 +1734,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>3</v>
@@ -1752,10 +1752,10 @@
         <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0342</v>
+        <v>0.0325</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,19 +1785,19 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>5.6</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0248</v>
+        <v>0.0342</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1839,25 +1839,25 @@
         <v>7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.0249</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>4.8</v>
@@ -1908,7 +1908,7 @@
         <v>3.6</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0224</v>
+        <v>0.0303</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>33.1</v>
+        <v>34.6</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>18.1</v>
+        <v>19.6</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,28 +1938,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L24" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0227</v>
+        <v>0.0192</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>32.9</v>
+        <v>33.8</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K25" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0287</v>
+        <v>0.0225</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,28 +2040,28 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0151</v>
+        <v>0.0229</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2094,25 +2094,25 @@
         <v>4.7</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.0289</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2145,25 +2145,25 @@
         <v>4.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.024</v>
+        <v>0.0151</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>30.6</v>
+        <v>32.5</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,28 +2193,28 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0206</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,28 +2244,28 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0322</v>
+        <v>0.0283</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>30.5</v>
+        <v>31.7</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>15.5</v>
+        <v>16.7</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>0</v>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0166</v>
+        <v>0.0335</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,28 +2346,28 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0177</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>30.1</v>
+        <v>30.5</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2400,25 +2400,25 @@
         <v>2.3</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0293</v>
+        <v>0.0322</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>4.8</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0166</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>2.4</v>
@@ -2508,19 +2508,19 @@
         <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.03</v>
+        <v>0.0218</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>2.4</v>
@@ -2565,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0248</v>
+        <v>0.0293</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>0</v>
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0208</v>
+        <v>0.0255</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2652,28 +2652,28 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0251</v>
+        <v>0.0248</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2706,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0445</v>
+        <v>0.0208</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>4.8</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0202</v>
+        <v>0.0251</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>28.3</v>
+        <v>29.4</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2805,28 +2805,28 @@
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0217</v>
+        <v>0.0447</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>28.1</v>
+        <v>29.3</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>13.1</v>
+        <v>14.3</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2862,7 +2862,7 @@
         <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0</v>
@@ -2871,13 +2871,13 @@
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.034</v>
+        <v>0.0204</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>12.6</v>
+        <v>13.3</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2907,28 +2907,28 @@
         <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0218</v>
+        <v>0.0219</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>6</v>
@@ -2976,10 +2976,10 @@
         <v>4.8</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0267</v>
+        <v>0.0209</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>27.2</v>
+        <v>28.1</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0193</v>
+        <v>0.034</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>26.9</v>
+        <v>27.6</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>11.9</v>
+        <v>12.6</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>6</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0337</v>
+        <v>0.0219</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>11.3</v>
+        <v>12.6</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         <v>1.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0233</v>
+        <v>0.0267</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.7</v>
+        <v>26.3</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3165,7 +3165,7 @@
         <v>2.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>0</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0229</v>
+        <v>0.0237</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,7 +3197,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.023</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3336,7 +3336,7 @@
         <v>3.6</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0349</v>
+        <v>0.0351</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-11T19:30:29.421080</t>
+          <t>2026-06-11T20:03:07.970295</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,25 +972,25 @@
         <v>7</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0398</v>
+        <v>0.0289</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>25.5</v>
+        <v>26.2</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1032,16 +1032,16 @@
         <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0398</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>39.6</v>
+        <v>40.5</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>24.6</v>
+        <v>25.5</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,7 +1074,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0345</v>
+        <v>0.02</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>4.2</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0502</v>
+        <v>0.0345</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1185,16 +1185,16 @@
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0247</v>
+        <v>0.0502</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>37.6</v>
+        <v>39.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>22.6</v>
+        <v>24.2</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,7 +1227,7 @@
         <v>4.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -1239,13 +1239,13 @@
         <v>2.1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0143</v>
+        <v>0.0247</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,7 +1259,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1296,7 +1296,7 @@
         <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0143</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0289</v>
+        <v>0.0283</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>35.2</v>
+        <v>35.5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>2.4</v>
@@ -1746,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>5.6</v>
@@ -1755,7 +1755,7 @@
         <v>4.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0325</v>
+        <v>0.0195</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1785,13 +1785,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>3</v>
@@ -1803,10 +1803,10 @@
         <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0342</v>
+        <v>0.0325</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,19 +1836,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>5.6</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0249</v>
+        <v>0.0342</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.0248</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -1953,13 +1953,13 @@
         <v>4.2</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.0303</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>18.8</v>
+        <v>19.6</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>6</v>
@@ -2001,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0225</v>
+        <v>0.0192</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>33.1</v>
+        <v>33.8</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2043,25 +2043,25 @@
         <v>2.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0229</v>
+        <v>0.0225</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>32.9</v>
+        <v>33.8</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0289</v>
+        <v>0.0335</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0151</v>
+        <v>0.0229</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2196,25 +2196,25 @@
         <v>4.7</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0289</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2247,7 +2247,7 @@
         <v>4.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
@@ -2259,13 +2259,13 @@
         <v>2.1</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0283</v>
+        <v>0.0151</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>16.7</v>
+        <v>17.5</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,28 +2295,28 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0335</v>
+        <v>0.0206</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-11T20:03:07.970295</t>
+          <t>2026-06-11T21:40:41.114870</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-11T21:40:41.114870</t>
+          <t>2026-06-11T21:57:22.302788</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>45.6</v>
+        <v>43.5</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>30.6</v>
+        <v>28.5</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -828,7 +828,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>5.6</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>6</v>
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>6</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -918,28 +918,28 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0302</v>
+        <v>0.0262</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -969,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.0301</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>34.9</v>
+        <v>36.7</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>19.9</v>
+        <v>21.7</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1023,25 +1023,25 @@
         <v>2.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.0357</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>34.2</v>
+        <v>34.9</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1071,28 +1071,28 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0261</v>
+        <v>0.0218</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1143,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0323</v>
+        <v>0.0322</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0143</v>
+        <v>0.0149</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>30.6</v>
+        <v>32.3</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>15.6</v>
+        <v>17.3</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,25 +1329,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0261</v>
+        <v>0.0209</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>29.3</v>
+        <v>30.6</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0204</v>
+        <v>0.026</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>26.4</v>
+        <v>29.3</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>4.8</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0175</v>
+        <v>0.0204</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>26.3</v>
+        <v>28.7</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1482,10 +1482,10 @@
         <v>4.7</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0216</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,10 +1530,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0388</v>
+        <v>0.0175</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>2.4</v>
@@ -1593,16 +1593,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0209</v>
+        <v>0.0196</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>23.9</v>
+        <v>25.3</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1632,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1644,16 +1644,16 @@
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0217</v>
+        <v>0.0387</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1704,7 +1704,7 @@
         <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0336</v>
+        <v>0.0333</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-12T06:43:44.143051</t>
+          <t>2026-06-12T09:02:23.989894</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-12T09:02:23.989894</t>
+          <t>2026-06-12T09:21:44.618109</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>40.6</v>
+        <v>43</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>25.6</v>
+        <v>28</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -867,28 +867,28 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.025</v>
+        <v>0.0184</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>37.4</v>
+        <v>40.6</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -918,28 +918,28 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0262</v>
+        <v>0.025</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37.3</v>
+        <v>39.7</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>22.3</v>
+        <v>24.7</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>4.7</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>4.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0301</v>
+        <v>0.0248</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>36.7</v>
+        <v>38.9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1020,28 +1020,28 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0357</v>
+        <v>0.0251</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>19.9</v>
+        <v>22.6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1071,28 +1071,28 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0218</v>
+        <v>0.0363</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>32.9</v>
+        <v>37.4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1122,13 +1122,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
         <v>4.8</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0322</v>
+        <v>0.0262</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>32.6</v>
+        <v>37.3</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>17.6</v>
+        <v>22.3</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1173,28 +1173,28 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0155</v>
+        <v>0.0301</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>32.6</v>
+        <v>36.8</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17.6</v>
+        <v>21.8</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1227,25 +1227,25 @@
         <v>4.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.0235</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>32.5</v>
+        <v>36.7</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17.5</v>
+        <v>21.7</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,28 +1275,28 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0357</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>32.3</v>
+        <v>35.3</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>17.3</v>
+        <v>20.3</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,28 +1326,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0538</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>30.6</v>
+        <v>34.9</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>15.6</v>
+        <v>19.9</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.026</v>
+        <v>0.0218</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>29.3</v>
+        <v>33.5</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>14.3</v>
+        <v>18.5</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
@@ -1440,16 +1440,16 @@
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0204</v>
+        <v>0.0142</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>28.7</v>
+        <v>32.9</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>13.7</v>
+        <v>17.9</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0216</v>
+        <v>0.0322</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>0006.HK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>26.4</v>
+        <v>32.9</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>11.4</v>
+        <v>17.9</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>4.8</v>
@@ -1548,10 +1548,10 @@
         <v>4.8</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0175</v>
+        <v>0.0254</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>26.3</v>
+        <v>32.9</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>11.3</v>
+        <v>17.9</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,10 +1581,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>0</v>
@@ -1593,16 +1593,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0318</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>25.3</v>
+        <v>32.6</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>10.3</v>
+        <v>17.6</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1635,7 +1635,7 @@
         <v>2.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
@@ -1644,16 +1644,16 @@
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0387</v>
+        <v>0.0155</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,49 +1667,1783 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>0941.HK</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>CA.PA</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>0857.HK</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>PUB.PA</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>0027.HK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>1928.HK</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>0388.HK</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>ML.PA</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>RI.PA</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>ORA.PA</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>SGO.PA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>1088.HK</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>RNO.PA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>0066.HK</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>BNP.PA</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ENGI.PA</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>1398.HK</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>0762.HK</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>EN.PA</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>ACA.PA</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>0386.HK</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>0939.HK</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>0151.HK</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>0101.HK</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>BN.PA</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="9" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
           <t>0883.HK</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B52" s="5" t="n">
         <v>23.3</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C52" s="5" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="8" t="n">
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G52" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="n">
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M52" s="6" t="n">
         <v>0.0333</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>6098.HK</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -1830,7 +3564,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-12T09:21:44.618109</t>
+          <t>2026-06-12T10:07:38.487343</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-12T10:07:38.487343</t>
+          <t>2026-06-12T10:25:53.197055</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-12T10:25:53.197055</t>
+          <t>2026-06-12T10:45:43.635091</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>43.5</v>
+        <v>48</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -822,13 +822,13 @@
         <v>6</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>5.6</v>
@@ -837,7 +837,7 @@
         <v>4.8</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0283</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>6</v>
@@ -876,19 +876,19 @@
         <v>4.8</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0184</v>
+        <v>0.0304</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>40.6</v>
+        <v>44.4</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>25.6</v>
+        <v>29.4</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -927,19 +927,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0254</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>ASRNL.AS</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39.7</v>
+        <v>43.6</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>24.7</v>
+        <v>28.6</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -969,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>4.2</v>
@@ -990,7 +990,7 @@
         <v>4.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0248</v>
+        <v>0.0149</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>38.9</v>
+        <v>42.1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>23.9</v>
+        <v>27.1</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1026,22 +1026,22 @@
         <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0251</v>
+        <v>0.0287</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>37.6</v>
+        <v>40.8</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>22.6</v>
+        <v>25.8</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1074,25 +1074,25 @@
         <v>7</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0363</v>
+        <v>0.0281</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>37.4</v>
+        <v>40.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0262</v>
+        <v>0.0248</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>37.3</v>
+        <v>40.6</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>22.3</v>
+        <v>25.6</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1176,16 +1176,16 @@
         <v>4.7</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>5.6</v>
@@ -1194,7 +1194,7 @@
         <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0301</v>
+        <v>0.0225</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>RNO.PA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>36.8</v>
+        <v>40.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>21.8</v>
+        <v>25.2</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1224,28 +1224,28 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0235</v>
+        <v>0.0344</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>36.7</v>
+        <v>39.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>21.7</v>
+        <v>24.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,28 +1275,28 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.0176</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>35.3</v>
+        <v>38.9</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>20.3</v>
+        <v>23.9</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1329,7 +1329,7 @@
         <v>4.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>3.6</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0538</v>
+        <v>0.0688</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>34.9</v>
+        <v>38.6</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>19.9</v>
+        <v>23.6</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0218</v>
+        <v>0.029</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>33.5</v>
+        <v>37.9</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>18.5</v>
+        <v>22.9</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>6</v>
@@ -1437,19 +1437,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0417</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>32.9</v>
+        <v>37.6</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>17.9</v>
+        <v>22.6</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1479,28 +1479,28 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0322</v>
+        <v>0.0455</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>0006.HK</t>
+          <t>DSFIR.AS</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>32.9</v>
+        <v>37.6</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>17.9</v>
+        <v>22.6</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,28 +1530,28 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0293</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>32.9</v>
+        <v>37.4</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,28 +1581,28 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0318</v>
+        <v>0.0156</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>SAN.PA</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>32.6</v>
+        <v>36.9</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>17.6</v>
+        <v>21.9</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1632,16 +1632,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>2.1</v>
@@ -1653,7 +1653,7 @@
         <v>3.6</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.0229</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>AKZA.AS</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>32.6</v>
+        <v>36.7</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>17.6</v>
+        <v>21.7</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1683,28 +1683,28 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.0584</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>32.5</v>
+        <v>35.8</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>17.5</v>
+        <v>20.8</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,25 +1734,25 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>0.0206</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>PHIA.AS</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>32.5</v>
+        <v>35.7</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>17.5</v>
+        <v>20.7</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,16 +1785,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0</v>
@@ -1803,10 +1803,10 @@
         <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.0228</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>CA.PA</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>32.4</v>
+        <v>34.2</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>17.4</v>
+        <v>19.2</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
@@ -1851,13 +1851,13 @@
         <v>4.2</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0217</v>
+        <v>0.0222</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>HEIA.AS</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>32.3</v>
+        <v>33.6</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0237</v>
+        <v>0.0236</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>0857.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,28 +1938,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0354</v>
+        <v>0.0281</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>PUB.PA</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>32</v>
+        <v>32.9</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,28 +1989,28 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L25" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0264</v>
+        <v>0.0283</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>30.6</v>
+        <v>32.9</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>15.6</v>
+        <v>17.9</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>6</v>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
@@ -2058,10 +2058,10 @@
         <v>4.8</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.026</v>
+        <v>0.0336</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>1928.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G27" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="M27" s="9" t="n">
-        <v>0.0323</v>
+        <v>0.0153</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>30.2</v>
+        <v>32.5</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>15.2</v>
+        <v>17.5</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.0213</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>ML.PA</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>30.2</v>
+        <v>31.9</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>15.2</v>
+        <v>16.9</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>2.4</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>4.2</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0203</v>
+        <v>0.0196</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>RI.PA</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,28 +2244,28 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0273</v>
+        <v>0.0319</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>29.7</v>
+        <v>31.2</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>14.7</v>
+        <v>16.2</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>0</v>
@@ -2310,13 +2310,13 @@
         <v>2.1</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0184</v>
+        <v>0.0193</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>SGO.PA</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>14.7</v>
+        <v>15.3</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2352,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>4.8</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0206</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>UNA.AS</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>29.6</v>
+        <v>30.3</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2397,28 +2397,28 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0302</v>
+        <v>0.018</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>RNO.PA</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,28 +2448,28 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0322</v>
+        <v>0.0255</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2502,7 +2502,7 @@
         <v>2.3</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>4.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0204</v>
+        <v>0.0312</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>0066.HK</t>
+          <t>1928.HK</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>29.3</v>
+        <v>28.2</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0191</v>
+        <v>0.0361</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>BNP.PA</t>
+          <t>6098.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>28.8</v>
+        <v>28.2</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2604,25 +2604,25 @@
         <v>0</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.02</v>
+        <v>0.0365</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>6</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0167</v>
+        <v>0.0228</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>28.7</v>
+        <v>27</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>13.7</v>
+        <v>12</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2703,28 +2703,28 @@
         <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0216</v>
+        <v>0.0167</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>0006.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>4.8</v>
@@ -2772,10 +2772,10 @@
         <v>4.8</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0252</v>
+        <v>0.0215</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>0762.HK</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>28.1</v>
+        <v>26.4</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2805,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0276</v>
+        <v>0.0305</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>27.9</v>
+        <v>26.4</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>12.9</v>
+        <v>11.4</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>0</v>
@@ -2868,16 +2868,16 @@
         <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0197</v>
+        <v>0.018</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>0151.HK</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>27.9</v>
+        <v>25.8</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
@@ -2919,16 +2919,16 @@
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0199</v>
+        <v>0.0333</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2961,10 +2961,10 @@
         <v>0</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0238</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,13 +3009,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I45" s="8" t="n">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0175</v>
+        <v>0.0352</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0857.HK</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>26.3</v>
+        <v>25.7</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3060,28 +3060,28 @@
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0375</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,13 +3111,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>0</v>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0387</v>
+        <v>0.0291</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>0151.HK</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>25.3</v>
+        <v>24.5</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0327</v>
+        <v>0.0357</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>0101.HK</t>
+          <t>0066.HK</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3213,10 +3213,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>0</v>
@@ -3225,16 +3225,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0221</v>
+        <v>0.0199</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>0762.HK</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3264,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0277</v>
+        <v>0.0268</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,25 +3318,25 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0192</v>
+        <v>0.0429</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,14 +3350,14 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>0101.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>15</v>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>2.4</v>
@@ -3381,69 +3381,18 @@
         <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0333</v>
+        <v>0.0233</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
       </c>
       <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>6098.HK</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="C53" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="9" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="N53" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -3564,7 +3513,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-12T10:45:43.635091</t>
+          <t>2026-06-16T07:26:07.003041</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>44.4</v>
+        <v>44.7</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -924,13 +924,13 @@
         <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>5.6</v>
@@ -939,7 +939,7 @@
         <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0329</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>ASRNL.AS</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -969,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>4.2</v>
@@ -987,10 +987,10 @@
         <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.0254</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>ASRNL.AS</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>42.1</v>
+        <v>43.6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>4.2</v>
@@ -1038,10 +1038,10 @@
         <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0287</v>
+        <v>0.0149</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>40.8</v>
+        <v>43.6</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>25.8</v>
+        <v>28.6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1080,19 +1080,19 @@
         <v>2.4</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0459</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40.6</v>
+        <v>42.1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>25.6</v>
+        <v>27.1</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1128,22 +1128,22 @@
         <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0248</v>
+        <v>0.0286</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>6</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>5.6</v>
@@ -1194,7 +1194,7 @@
         <v>4.8</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0225</v>
+        <v>0.0281</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>RNO.PA</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>2.1</v>
@@ -1242,10 +1242,10 @@
         <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0344</v>
+        <v>0.0248</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>39.6</v>
+        <v>40.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>6</v>
@@ -1296,7 +1296,7 @@
         <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0176</v>
+        <v>0.0225</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>6</v>
@@ -1335,19 +1335,19 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0688</v>
+        <v>0.0333</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>RNO.PA</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>38.6</v>
+        <v>40.2</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>23.6</v>
+        <v>25.2</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.029</v>
+        <v>0.0344</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>37.9</v>
+        <v>39.6</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,28 +1428,28 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0417</v>
+        <v>0.0176</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>37.6</v>
+        <v>38.9</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>3.6</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0455</v>
+        <v>0.0688</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>DSFIR.AS</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,28 +1530,28 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.029</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>37.4</v>
+        <v>37.9</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,25 +1584,25 @@
         <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0294</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SAN.PA</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>36.9</v>
+        <v>37.9</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1632,28 +1632,28 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0229</v>
+        <v>0.0417</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>AKZA.AS</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1683,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2.4</v>
@@ -1701,10 +1701,10 @@
         <v>2.4</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0584</v>
+        <v>0.0455</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>DSFIR.AS</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>35.8</v>
+        <v>37.6</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>20.8</v>
+        <v>22.6</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0293</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>PHIA.AS</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>35.7</v>
+        <v>37.4</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>20.7</v>
+        <v>22.4</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>2.4</v>
@@ -1797,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0228</v>
+        <v>0.0156</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>SAN.PA</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>34.2</v>
+        <v>36.9</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>19.2</v>
+        <v>21.9</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,28 +1836,28 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0229</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>HEIA.AS</t>
+          <t>AKZA.AS</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>33.6</v>
+        <v>36.7</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>18.6</v>
+        <v>21.7</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1899,16 +1899,16 @@
         <v>3</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0236</v>
+        <v>0.0584</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>33</v>
+        <v>36.6</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>18</v>
+        <v>21.6</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,28 +1938,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0281</v>
+        <v>0.0344</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>17.9</v>
+        <v>20.8</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>6</v>
@@ -1998,19 +1998,19 @@
         <v>2.4</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L25" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0283</v>
+        <v>0.0206</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>17.9</v>
+        <v>20.8</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,28 +2040,28 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.0341</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>PHIA.AS</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>32.6</v>
+        <v>35.7</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>17.6</v>
+        <v>20.7</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0153</v>
+        <v>0.0228</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>32.5</v>
+        <v>34.7</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>17.5</v>
+        <v>19.7</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0322</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>31.9</v>
+        <v>34.2</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>16.9</v>
+        <v>19.2</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>2.4</v>
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0222</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>HEIA.AS</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>31.7</v>
+        <v>33.6</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>16.7</v>
+        <v>18.6</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,28 +2244,28 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0319</v>
+        <v>0.0236</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>31.2</v>
+        <v>33</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>2.4</v>
@@ -2307,16 +2307,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0193</v>
+        <v>0.0281</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>30.3</v>
+        <v>32.9</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>15.3</v>
+        <v>17.9</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>6</v>
@@ -2355,19 +2355,19 @@
         <v>2.4</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0283</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>UNA.AS</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>30.3</v>
+        <v>32.9</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>15.3</v>
+        <v>17.9</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2397,13 +2397,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>3</v>
@@ -2412,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.018</v>
+        <v>0.0336</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>29.2</v>
+        <v>32.8</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>14.2</v>
+        <v>17.8</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,28 +2448,28 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0255</v>
+        <v>0.0293</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>28.7</v>
+        <v>32.6</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>13.7</v>
+        <v>17.6</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2502,7 +2502,7 @@
         <v>2.3</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0312</v>
+        <v>0.0153</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>1928.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>28.2</v>
+        <v>32.5</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>13.2</v>
+        <v>17.5</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,28 +2550,28 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0361</v>
+        <v>0.0213</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>6098.HK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>28.2</v>
+        <v>32.1</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>13.2</v>
+        <v>17.1</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2613,16 +2613,16 @@
         <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0365</v>
+        <v>0.0226</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>28.1</v>
+        <v>31.9</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>13.1</v>
+        <v>16.9</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2652,10 +2652,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0</v>
@@ -2664,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0228</v>
+        <v>0.0196</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>27</v>
+        <v>31.7</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2703,28 +2703,28 @@
         <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0167</v>
+        <v>0.0319</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>0006.HK</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>26.9</v>
+        <v>31.6</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>11.9</v>
+        <v>16.6</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,28 +2754,28 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0314</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>26.4</v>
+        <v>31.2</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>11.4</v>
+        <v>16.2</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2.4</v>
@@ -2817,16 +2817,16 @@
         <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0305</v>
+        <v>0.0193</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>UNA.AS</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>26.4</v>
+        <v>30.3</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>11.4</v>
+        <v>15.3</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2856,25 +2856,25 @@
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
         <v>0.018</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>0151.HK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>25.8</v>
+        <v>30.1</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>10.8</v>
+        <v>15.1</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2907,28 +2907,28 @@
         <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.0378</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>0386.HK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>25.8</v>
+        <v>29.3</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>10.8</v>
+        <v>14.3</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>0</v>
@@ -2973,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0238</v>
+        <v>0.0246</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>25.7</v>
+        <v>29.2</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>10.7</v>
+        <v>14.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0352</v>
+        <v>0.0255</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0857.HK</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>25.7</v>
+        <v>28.7</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>10.7</v>
+        <v>13.7</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
         <v>2.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>0</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0375</v>
+        <v>0.0312</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>1928.HK</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>24.6</v>
+        <v>28.2</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>2.4</v>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0291</v>
+        <v>0.036</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>24.5</v>
+        <v>28.2</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3162,13 +3162,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0357</v>
+        <v>0.0206</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>0066.HK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>24.2</v>
+        <v>28.1</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3216,16 +3216,16 @@
         <v>2.3</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>2.4</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0199</v>
+        <v>0.0284</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>0762.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>23.9</v>
+        <v>28.1</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>8.9</v>
+        <v>13.1</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3267,10 +3267,10 @@
         <v>2.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0268</v>
+        <v>0.0228</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>23.4</v>
+        <v>27</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3315,28 +3315,28 @@
         <v>0</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0429</v>
+        <v>0.0167</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,49 +3350,712 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>0006.HK</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M53" s="9" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>0003.HK</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>0151.HK</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>0386.HK</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>0883.HK</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M57" s="9" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>0066.HK</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>0857.HK</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2318.HK</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>6098.HK</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>1299.HK</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>0762.HK</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M63" s="9" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>0700.HK</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="6" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>BEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
           <t>0101.HK</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B65" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C65" s="8" t="n">
         <v>7.2</v>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="6" t="n">
+      <c r="D65" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="9" t="n">
         <v>0.0233</v>
       </c>
-      <c r="N52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="N65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -3513,7 +4176,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T07:26:07.003041</t>
+          <t>2026-06-16T07:32:06.174443</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ASRNL.AS</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>48</v>
+        <v>43.6</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>33</v>
+        <v>28.6</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>6</v>
@@ -825,7 +825,7 @@
         <v>2.4</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>4.2</v>
@@ -837,7 +837,7 @@
         <v>4.8</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0283</v>
+        <v>0.0149</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>46</v>
+        <v>43.5</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>31</v>
+        <v>28.5</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -873,22 +873,22 @@
         <v>6</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0304</v>
+        <v>0.0268</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>44.7</v>
+        <v>43.2</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>29.7</v>
+        <v>28.2</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,25 +921,25 @@
         <v>7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0329</v>
+        <v>0.0366</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>44.4</v>
+        <v>42.6</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>29.4</v>
+        <v>27.6</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -987,7 +987,7 @@
         <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0.0254</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ASRNL.AS</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>43.6</v>
+        <v>42.1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>28.6</v>
+        <v>27.1</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>4.2</v>
@@ -1038,10 +1038,10 @@
         <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.0284</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>43.6</v>
+        <v>41.3</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>28.6</v>
+        <v>26.3</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>3</v>
@@ -1086,13 +1086,13 @@
         <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0459</v>
+        <v>0.048</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>42.1</v>
+        <v>40.8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>3.6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.0278</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1173,28 +1173,28 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0249</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>RNO.PA</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>40.6</v>
+        <v>40.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>2.1</v>
@@ -1242,10 +1242,10 @@
         <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0248</v>
+        <v>0.0344</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>40.6</v>
+        <v>39.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>25.6</v>
+        <v>24.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>6</v>
@@ -1296,7 +1296,7 @@
         <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0225</v>
+        <v>0.0176</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>6</v>
@@ -1335,19 +1335,19 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0333</v>
+        <v>0.0282</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1361,14 +1361,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>RNO.PA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>40.2</v>
+        <v>38.9</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>25.2</v>
+        <v>23.9</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>15</v>
@@ -1377,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>0.0344</v>
+        <v>0.0383</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>39.6</v>
+        <v>37.9</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>24.6</v>
+        <v>22.9</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1428,28 +1428,28 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0176</v>
+        <v>0.0323</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DSFIR.AS</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>38.9</v>
+        <v>37.6</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>23.9</v>
+        <v>22.6</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>0</v>
@@ -1494,13 +1494,13 @@
         <v>4.2</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0688</v>
+        <v>0.0293</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>38.6</v>
+        <v>37.6</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,28 +1530,28 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.029</v>
+        <v>0.0201</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1584,25 +1584,25 @@
         <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0294</v>
+        <v>0.0156</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1635,25 +1635,25 @@
         <v>4.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0417</v>
+        <v>0.0195</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SAN.PA</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>37.6</v>
+        <v>36.9</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1683,28 +1683,28 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0455</v>
+        <v>0.0229</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>DSFIR.AS</t>
+          <t>AKZA.AS</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>37.6</v>
+        <v>36.7</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>2.4</v>
@@ -1749,13 +1749,13 @@
         <v>4.2</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.0584</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>37.4</v>
+        <v>36.1</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1788,25 +1788,25 @@
         <v>4.7</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0183</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SAN.PA</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>36.9</v>
+        <v>35.8</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>21.9</v>
+        <v>20.8</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>6</v>
@@ -1845,7 +1845,7 @@
         <v>2.4</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>2.1</v>
@@ -1854,10 +1854,10 @@
         <v>4.8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0229</v>
+        <v>0.0206</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>AKZA.AS</t>
+          <t>PHIA.AS</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>36.7</v>
+        <v>35.7</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>21.7</v>
+        <v>20.7</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0584</v>
+        <v>0.0228</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>36.6</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>21.6</v>
+        <v>20</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -1950,16 +1950,16 @@
         <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0344</v>
+        <v>0.022</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>35.8</v>
+        <v>34.9</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,28 +1989,28 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0213</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>35.8</v>
+        <v>34.8</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>20.8</v>
+        <v>19.8</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>5.6</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0341</v>
+        <v>0.0205</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>PHIA.AS</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>35.7</v>
+        <v>34.8</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K27" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0228</v>
+        <v>0.0255</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2148,22 +2148,22 @@
         <v>6</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0322</v>
+        <v>0.0241</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>2.4</v>
@@ -2202,19 +2202,19 @@
         <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.0276</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>HEIA.AS</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>33.6</v>
+        <v>34.2</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>2.4</v>
@@ -2253,19 +2253,19 @@
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0236</v>
+        <v>0.0222</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>33</v>
+        <v>34.1</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>2.4</v>
@@ -2316,7 +2316,7 @@
         <v>4.8</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0318</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>1928.HK</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>32.9</v>
+        <v>33.8</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,28 +2346,28 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0283</v>
+        <v>0.0359</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>HEIA.AS</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>32.9</v>
+        <v>33.6</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0</v>
@@ -2409,16 +2409,16 @@
         <v>3</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0336</v>
+        <v>0.0236</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2454,22 +2454,22 @@
         <v>2.4</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.0225</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2499,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0153</v>
+        <v>0.0281</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0</v>
@@ -2562,16 +2562,16 @@
         <v>3</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0336</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2601,28 +2601,28 @@
         <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L37" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L37" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M37" s="9" t="n">
-        <v>0.0226</v>
+        <v>0.0195</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2652,28 +2652,28 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.02</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>31.7</v>
+        <v>32.3</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2703,10 +2703,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>4.8</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0319</v>
+        <v>0.0257</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>16.6</v>
+        <v>17.3</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,28 +2754,28 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J40" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0314</v>
+        <v>0.0262</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>UNA.AS</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>30.3</v>
+        <v>31.1</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>15.3</v>
+        <v>16.1</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2856,28 +2856,28 @@
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.018</v>
+        <v>0.0312</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>30.1</v>
+        <v>30.8</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2913,22 +2913,22 @@
         <v>2.4</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0378</v>
+        <v>0.0153</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>UNA.AS</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>2.4</v>
@@ -2967,19 +2967,19 @@
         <v>2.4</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0246</v>
+        <v>0.018</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>29.2</v>
+        <v>30.2</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>14.2</v>
+        <v>15.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0255</v>
+        <v>0.0289</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3060,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>1.8</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0179</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>1928.HK</t>
+          <t>0762.HK</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>2.4</v>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.036</v>
+        <v>0.0266</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3162,28 +3162,28 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0255</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>6</v>
@@ -3228,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0284</v>
+        <v>0.0206</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>6098.HK</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3264,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0228</v>
+        <v>0.0364</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>27</v>
+        <v>28.1</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3315,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>2.4</v>
@@ -3327,16 +3327,16 @@
         <v>0</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0167</v>
+        <v>0.0289</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,14 +3350,14 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>0006.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>15</v>
@@ -3366,28 +3366,28 @@
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0167</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,14 +3401,14 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>0006.HK</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>15</v>
@@ -3417,13 +3417,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>0</v>
@@ -3435,10 +3435,10 @@
         <v>4.8</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.0305</v>
+        <v>0.0215</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>0066.HK</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3468,13 +3468,13 @@
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>0</v>
@@ -3486,10 +3486,10 @@
         <v>4.8</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0179</v>
+        <v>0.0199</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,14 +3503,14 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>0151.HK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>10.8</v>
+        <v>11.6</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>15</v>
@@ -3519,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
@@ -3531,16 +3531,16 @@
         <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.0232</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,7 +3554,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>0386.HK</t>
+          <t>0151.HK</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0238</v>
+        <v>0.0332</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,14 +3605,14 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>0386.HK</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>15</v>
@@ -3621,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>2.4</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0352</v>
+        <v>0.0237</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>0066.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0198</v>
+        <v>0.0195</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,7 +3707,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>0857.HK</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -3744,7 +3744,7 @@
         <v>3.6</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.0348</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,14 +3758,14 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>0857.HK</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>15</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>2.4</v>
@@ -3789,13 +3789,13 @@
         <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.029</v>
+        <v>0.0371</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,14 +3809,14 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>6098.HK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>15</v>
@@ -3825,13 +3825,13 @@
         <v>0</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
         <v>0</v>
@@ -3840,13 +3840,13 @@
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0366</v>
+        <v>0.0282</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.0355</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
@@ -3911,14 +3911,14 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>0762.HK</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>15</v>
@@ -3927,13 +3927,13 @@
         <v>0</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I63" s="8" t="n">
         <v>0</v>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L63" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>0.0269</v>
+        <v>0.0261</v>
       </c>
       <c r="N63" s="8" t="n">
         <v>1</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T07:32:06.174443</t>
+          <t>2026-06-16T18:42:04.192160</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -800,14 +800,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ASRNL.AS</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>43.6</v>
+        <v>46.8</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>15</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>6</v>
@@ -825,7 +825,7 @@
         <v>2.4</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>4.2</v>
@@ -834,10 +834,10 @@
         <v>5.6</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.0351</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1</v>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ASRNL.AS</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" s="8" t="n">
         <v>5.6</v>
@@ -888,7 +888,7 @@
         <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0268</v>
+        <v>0.0149</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>43.2</v>
+        <v>42.6</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,7 +921,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0366</v>
+        <v>0.0254</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>42.6</v>
+        <v>41.6</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>27.6</v>
+        <v>26.6</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -969,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.0281</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>42.1</v>
+        <v>41.3</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>27.1</v>
+        <v>26.3</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1035,13 +1035,13 @@
         <v>4.2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.0487</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -1077,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>3</v>
@@ -1086,13 +1086,13 @@
         <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.048</v>
+        <v>0.0238</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1173,13 +1173,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0</v>
@@ -1188,13 +1188,13 @@
         <v>4.2</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0249</v>
+        <v>0.0271</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,16 +1275,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>2.1</v>
@@ -1293,10 +1293,10 @@
         <v>5.6</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0176</v>
+        <v>0.0284</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>ENGI.PA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>39.2</v>
+        <v>39.6</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,28 +1326,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K12" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M12" s="6" t="n">
-        <v>0.0282</v>
+        <v>0.0176</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1412,14 +1412,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>15</v>
@@ -1437,19 +1437,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.0323</v>
+        <v>0.0249</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>DSFIR.AS</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>37.6</v>
+        <v>38.5</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>22.6</v>
+        <v>23.5</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1479,19 +1479,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>5.6</v>
@@ -1500,7 +1500,7 @@
         <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0293</v>
+        <v>0.0182</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,7 +1514,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DSFIR.AS</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>2.4</v>
@@ -1542,16 +1542,16 @@
         <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0201</v>
+        <v>0.0293</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,7 +1565,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1584,25 +1584,25 @@
         <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0222</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1635,25 +1635,25 @@
         <v>4.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0195</v>
+        <v>0.0156</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>SAN.PA</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>2.4</v>
@@ -1695,16 +1695,16 @@
         <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0229</v>
+        <v>0.0195</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>AKZA.AS</t>
+          <t>SAN.PA</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0584</v>
+        <v>0.0229</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>AKZA.AS</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>36.1</v>
+        <v>36.7</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>0</v>
@@ -1797,16 +1797,16 @@
         <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0584</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1947,19 +1947,19 @@
         <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.022</v>
+        <v>0.0264</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>34.9</v>
+        <v>35.3</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1992,25 +1992,25 @@
         <v>4.7</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0213</v>
+        <v>0.0195</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>5.6</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.02</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,13 +2091,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>3</v>
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0255</v>
+        <v>0.0213</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>34.4</v>
+        <v>34.8</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
@@ -2154,16 +2154,16 @@
         <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0241</v>
+        <v>0.0254</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>34.3</v>
+        <v>34.7</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
@@ -2208,13 +2208,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0276</v>
+        <v>0.0329</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>2.4</v>
@@ -2253,19 +2253,19 @@
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0276</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,28 +2295,28 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0318</v>
+        <v>0.0222</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>1928.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0</v>
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0359</v>
+        <v>0.0318</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>HEIA.AS</t>
+          <t>1928.HK</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2397,28 +2397,28 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0236</v>
+        <v>0.0359</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>HEIA.AS</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>2.4</v>
@@ -2460,16 +2460,16 @@
         <v>3</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0225</v>
+        <v>0.0236</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2499,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0226</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
@@ -2568,10 +2568,10 @@
         <v>4.8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.0281</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,7 +2585,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>6</v>
@@ -2610,19 +2610,19 @@
         <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0336</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>17.3</v>
+        <v>16.2</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2703,28 +2703,28 @@
         <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0257</v>
+        <v>0.0193</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>32.3</v>
+        <v>31.1</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>17.3</v>
+        <v>16.1</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,28 +2754,28 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0262</v>
+        <v>0.0312</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>2.4</v>
@@ -2820,13 +2820,13 @@
         <v>2.1</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0193</v>
+        <v>0.0153</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>UNA.AS</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>31.1</v>
+        <v>30.3</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2856,28 +2856,28 @@
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.018</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2907,28 +2907,28 @@
         <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0153</v>
+        <v>0.0289</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>UNA.AS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2958,28 +2958,28 @@
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.018</v>
+        <v>0.0257</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>30.2</v>
+        <v>29.2</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0289</v>
+        <v>0.0205</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3162,28 +3162,28 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0255</v>
+        <v>0.0206</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,7 +3197,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>6098.HK</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0364</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>6098.HK</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>6</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0288</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>28.1</v>
+        <v>27.5</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0289</v>
+        <v>0.0281</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0232</v>
+        <v>0.0231</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,14 +3554,14 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>0151.HK</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>15</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>0</v>
@@ -3588,10 +3588,10 @@
         <v>4.8</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0332</v>
+        <v>0.0262</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,7 +3605,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>0386.HK</t>
+          <t>0151.HK</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -3627,7 +3627,7 @@
         <v>6</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I57" s="8" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L57" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0237</v>
+        <v>0.0332</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,14 +3656,14 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0386.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>15</v>
@@ -3672,13 +3672,13 @@
         <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0195</v>
+        <v>0.0237</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,7 +3707,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -3726,10 +3726,10 @@
         <v>2.3</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0348</v>
+        <v>0.0195</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>0857.HK</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -3795,7 +3795,7 @@
         <v>3.6</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0371</v>
+        <v>0.0348</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,14 +3809,14 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>0857.HK</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>25.1</v>
+        <v>25.7</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>15</v>
@@ -3828,10 +3828,10 @@
         <v>2.3</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I61" s="8" t="n">
         <v>0</v>
@@ -3843,10 +3843,10 @@
         <v>0</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0282</v>
+        <v>0.0371</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
@@ -3911,14 +3911,14 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>15</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>0</v>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>0.0261</v>
+        <v>0.0429</v>
       </c>
       <c r="N63" s="8" t="n">
         <v>1</v>
@@ -3962,14 +3962,14 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>23.4</v>
+        <v>22.7</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>15</v>
@@ -3978,28 +3978,28 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>0.0429</v>
+        <v>0.0254</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>1</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T18:42:04.192160</t>
+          <t>2026-06-16T19:59:11.606752</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>42.6</v>
+        <v>43.2</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -921,10 +921,10 @@
         <v>7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>3</v>
@@ -936,10 +936,10 @@
         <v>5.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0279</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>41.6</v>
+        <v>42.6</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -969,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0254</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1026,13 +1026,13 @@
         <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>4.8</v>
@@ -1041,7 +1041,7 @@
         <v>3.6</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0487</v>
+        <v>0.0281</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -1077,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>3</v>
@@ -1086,13 +1086,13 @@
         <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0238</v>
+        <v>0.0488</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40.8</v>
+        <v>41.3</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1122,13 +1122,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>3</v>
@@ -1137,13 +1137,13 @@
         <v>4.2</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0278</v>
+        <v>0.0238</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>1.8</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0182</v>
+        <v>0.0183</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>DSFIR.AS</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1530,16 +1530,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>4.2</v>
@@ -1548,10 +1548,10 @@
         <v>5.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0293</v>
+        <v>0.0264</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>DSFIR.AS</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,28 +1581,28 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.0293</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,7 +1616,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -1635,25 +1635,25 @@
         <v>4.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0156</v>
+        <v>0.0222</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,25 +1686,25 @@
         <v>4.7</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0156</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>SAN.PA</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>2.4</v>
@@ -1746,16 +1746,16 @@
         <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0229</v>
+        <v>0.0195</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>AKZA.AS</t>
+          <t>SAN.PA</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,28 +1785,28 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0584</v>
+        <v>0.0229</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>AKZA.AS</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>35.8</v>
+        <v>36.7</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1839,25 +1839,25 @@
         <v>3.7</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M22" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0584</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>PHIA.AS</t>
+          <t>ORA.PA</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>6</v>
@@ -1899,16 +1899,16 @@
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0228</v>
+        <v>0.0206</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PHIA.AS</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,28 +1938,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0264</v>
+        <v>0.0228</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0213</v>
+        <v>0.02</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>3</v>
@@ -2163,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0213</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>0</v>
@@ -2205,16 +2205,16 @@
         <v>3</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0329</v>
+        <v>0.0254</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>34.3</v>
+        <v>34.7</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0</v>
@@ -2259,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0329</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>2.4</v>
@@ -2304,19 +2304,19 @@
         <v>0</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.0277</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>0016.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,28 +2346,28 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0318</v>
+        <v>0.0222</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2381,14 +2381,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>1928.HK</t>
+          <t>0016.HK</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2397,13 +2397,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>0</v>
@@ -2412,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0359</v>
+        <v>0.0318</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>HEIA.AS</t>
+          <t>1928.HK</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,28 +2448,28 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0236</v>
+        <v>0.0359</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>HEIA.AS</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2499,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0226</v>
+        <v>0.0236</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,28 +2550,28 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0281</v>
+        <v>0.0227</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2601,16 +2601,16 @@
         <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>4.8</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0336</v>
+        <v>0.0281</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2652,28 +2652,28 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0336</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>31.2</v>
+        <v>32.3</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>16.2</v>
+        <v>17.3</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2703,28 +2703,28 @@
         <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0193</v>
+        <v>0.0258</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>EN.PA</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>2.4</v>
@@ -2766,16 +2766,16 @@
         <v>0</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0312</v>
+        <v>0.0193</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2808,7 +2808,7 @@
         <v>2.3</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>2.4</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>4.8</v>
@@ -2826,7 +2826,7 @@
         <v>1.8</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0153</v>
+        <v>0.0312</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>UNA.AS</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>30.3</v>
+        <v>30.8</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>2.4</v>
@@ -2865,19 +2865,19 @@
         <v>2.4</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.018</v>
+        <v>0.0153</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2907,13 +2907,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
@@ -2922,13 +2922,13 @@
         <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" s="9" t="n">
-        <v>0.0289</v>
+        <v>0.0281</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>0</v>
@@ -2976,10 +2976,10 @@
         <v>2.4</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0257</v>
+        <v>0.0288</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>UNA.AS</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>29.2</v>
+        <v>30.3</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I45" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.018</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>28.8</v>
+        <v>30.2</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>13.8</v>
+        <v>15.2</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>0</v>
@@ -3078,10 +3078,10 @@
         <v>4.8</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0179</v>
+        <v>0.0289</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>0762.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,28 +3111,28 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0266</v>
+        <v>0.0205</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>28.2</v>
+        <v>29</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3162,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>2.4</v>
@@ -3174,16 +3174,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.0232</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>6098.HK</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>2.4</v>
@@ -3231,10 +3231,10 @@
         <v>4.8</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0364</v>
+        <v>0.0179</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>0762.HK</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3267,7 +3267,7 @@
         <v>2.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>2.4</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0288</v>
+        <v>0.0266</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>6</v>
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0206</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,14 +3350,14 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>6098.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>27</v>
+        <v>28.2</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>15</v>
@@ -3366,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>2.4</v>
@@ -3378,16 +3378,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0167</v>
+        <v>0.0364</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,14 +3401,14 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>0006.HK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>26.9</v>
+        <v>28.1</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>15</v>
@@ -3420,10 +3420,10 @@
         <v>2.3</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>0</v>
@@ -3432,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.0215</v>
+        <v>0.0195</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>0066.HK</t>
+          <t>ACA.PA</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3468,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="5" t="n">
         <v>2.4</v>
@@ -3480,16 +3480,16 @@
         <v>0</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0199</v>
+        <v>0.0167</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,14 +3503,14 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>0006.HK</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>15</v>
@@ -3519,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
@@ -3531,16 +3531,16 @@
         <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0231</v>
+        <v>0.0215</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,14 +3554,14 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>0066.HK</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>15</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>2.4</v>
@@ -3588,10 +3588,10 @@
         <v>4.8</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0262</v>
+        <v>0.0199</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,14 +3605,14 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>0151.HK</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>15</v>
@@ -3624,10 +3624,10 @@
         <v>0</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I57" s="8" t="n">
         <v>0</v>
@@ -3639,10 +3639,10 @@
         <v>4.8</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0332</v>
+        <v>0.0262</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>0386.HK</t>
+          <t>0151.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -3678,7 +3678,7 @@
         <v>6</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>0</v>
@@ -3687,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0237</v>
+        <v>0.0332</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0386.HK</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -3723,13 +3723,13 @@
         <v>0</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I59" s="8" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0237</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3860,14 +3860,14 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>15</v>
@@ -3882,22 +3882,22 @@
         <v>2.4</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0355</v>
+        <v>0.0254</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
@@ -3911,14 +3911,14 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>23.4</v>
+        <v>24.5</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>15</v>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>0</v>
@@ -3942,13 +3942,13 @@
         <v>0</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L63" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>0.0429</v>
+        <v>0.0355</v>
       </c>
       <c r="N63" s="8" t="n">
         <v>1</v>
@@ -3962,14 +3962,14 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>15</v>
@@ -3978,28 +3978,28 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0429</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>1</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T19:59:11.606752</t>
+          <t>2026-06-16T21:36:45.500705</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T21:36:45.500705</t>
+          <t>2026-06-16T22:04:57.483298</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T22:04:57.483298</t>
+          <t>2026-06-16T22:24:40.598438</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -851,14 +851,14 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>ASRNL.AS</t>
+          <t>AGN.AS</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>43.6</v>
+        <v>46.6</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>28.6</v>
+        <v>31.6</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>15</v>
@@ -876,7 +876,7 @@
         <v>2.4</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>4.2</v>
@@ -888,7 +888,7 @@
         <v>4.8</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.017</v>
       </c>
       <c r="N3" s="8" t="n">
         <v>1</v>
@@ -902,14 +902,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VPK.AS</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>43.2</v>
+        <v>43.8</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>15</v>
@@ -918,28 +918,28 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.0279</v>
+        <v>0.0154</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>1</v>
@@ -953,14 +953,14 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>42.6</v>
+        <v>43.2</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>15</v>
@@ -972,10 +972,10 @@
         <v>7</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>3</v>
@@ -987,10 +987,10 @@
         <v>5.6</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.0279</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>1</v>
@@ -1004,14 +1004,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>41.6</v>
+        <v>42.6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26.6</v>
+        <v>27.6</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>15</v>
@@ -1020,28 +1020,28 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.0281</v>
+        <v>0.0271</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>1</v>
@@ -1055,14 +1055,14 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>41.3</v>
+        <v>42.6</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>15</v>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>6</v>
@@ -1086,13 +1086,13 @@
         <v>4.2</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.0488</v>
+        <v>0.0244</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>1</v>
@@ -1106,14 +1106,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>15</v>
@@ -1134,16 +1134,16 @@
         <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.0238</v>
+        <v>0.0281</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>1</v>
@@ -1157,14 +1157,14 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>40.2</v>
+        <v>41.3</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>15</v>
@@ -1173,28 +1173,28 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>4.2</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0271</v>
+        <v>0.0488</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>1</v>
@@ -1208,14 +1208,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>RNO.PA</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>15</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>2.1</v>
@@ -1242,10 +1242,10 @@
         <v>5.6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0.0344</v>
+        <v>0.0183</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>1</v>
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9999.HK</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1281,7 +1281,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>3</v>
@@ -1293,10 +1293,10 @@
         <v>5.6</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0284</v>
+        <v>0.0337</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ENGI.PA</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,28 +1326,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0176</v>
+        <v>0.0205</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1463,14 +1463,14 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>38.5</v>
+        <v>37.9</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>23.5</v>
+        <v>22.9</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>15</v>
@@ -1488,19 +1488,19 @@
         <v>2.4</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K15" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0.0183</v>
+        <v>0.0264</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>1</v>
@@ -1514,14 +1514,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>15</v>
@@ -1539,19 +1539,19 @@
         <v>2.4</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.0264</v>
+        <v>0.0222</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>1</v>
@@ -1565,14 +1565,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>DSFIR.AS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>15</v>
@@ -1581,28 +1581,28 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.0293</v>
+        <v>0.0195</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>1</v>
@@ -1616,14 +1616,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>15</v>
@@ -1644,16 +1644,16 @@
         <v>3</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0329</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>1</v>
@@ -1667,14 +1667,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>9999.HK</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>37.4</v>
+        <v>36.8</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>15</v>
@@ -1686,25 +1686,25 @@
         <v>4.7</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.028</v>
       </c>
       <c r="N19" s="8" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>22.3</v>
+        <v>20.4</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0195</v>
+        <v>0.0376</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>SAN.PA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>36.9</v>
+        <v>35.2</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>21.9</v>
+        <v>20.2</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>2.4</v>
@@ -1800,13 +1800,13 @@
         <v>2.1</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0.0229</v>
+        <v>0.02</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>1</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>AKZA.AS</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>36.7</v>
+        <v>35.1</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,28 +1836,28 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.0584</v>
+        <v>0.02</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>ORA.PA</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>35.8</v>
+        <v>34.9</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0198</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>PHIA.AS</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>35.7</v>
+        <v>34.8</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,28 +1938,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0228</v>
+        <v>0.0254</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>35.3</v>
+        <v>34.7</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>20.3</v>
+        <v>19.7</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -2004,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0258</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>35.2</v>
+        <v>34.3</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>20.2</v>
+        <v>19.3</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2040,28 +2040,28 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0277</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>35.1</v>
+        <v>34.1</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>20.1</v>
+        <v>19.1</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.02</v>
+        <v>0.0336</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>1398.HK</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>34.9</v>
+        <v>33.4</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>19.9</v>
+        <v>18.4</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0276</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>34.8</v>
+        <v>33.1</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,28 +2193,28 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0254</v>
+        <v>0.0227</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>PRX.AS</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>34.7</v>
+        <v>33</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>19.7</v>
+        <v>18</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>3</v>
@@ -2259,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0329</v>
+        <v>0.0344</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>34.3</v>
+        <v>32.7</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>19.3</v>
+        <v>17.7</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>2.4</v>
@@ -2313,10 +2313,10 @@
         <v>5.6</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0277</v>
+        <v>0.0194</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2330,14 +2330,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>1398.HK</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>34.2</v>
+        <v>32.5</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>19.2</v>
+        <v>17.5</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>15</v>
@@ -2346,16 +2346,16 @@
         <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>4.2</v>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0208</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>34.1</v>
+        <v>31.7</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>19.1</v>
+        <v>16.7</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>15</v>
@@ -2403,7 +2403,7 @@
         <v>4.8</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>4.8</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>0.0318</v>
+        <v>0.0316</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>1</v>
@@ -2432,14 +2432,14 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>1928.HK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>33.8</v>
+        <v>31.6</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>18.8</v>
+        <v>16.6</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>15</v>
@@ -2448,28 +2448,28 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0.0359</v>
+        <v>0.0205</v>
       </c>
       <c r="N34" s="5" t="n">
         <v>1</v>
@@ -2483,14 +2483,14 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>HEIA.AS</t>
+          <t>RI.PA</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>33.6</v>
+        <v>31.3</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>18.6</v>
+        <v>16.3</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>15</v>
@@ -2499,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.0236</v>
+        <v>0.0274</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>1</v>
@@ -2534,14 +2534,14 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>VIE.PA</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>33.1</v>
+        <v>30.7</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>18.1</v>
+        <v>15.7</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>15</v>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>2.4</v>
@@ -2562,16 +2562,16 @@
         <v>3</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.0227</v>
+        <v>0.0152</v>
       </c>
       <c r="N36" s="5" t="n">
         <v>1</v>
@@ -2585,14 +2585,14 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>0027.HK</t>
+          <t>1928.HK</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>33</v>
+        <v>30.6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>18</v>
+        <v>15.6</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>15</v>
@@ -2607,7 +2607,7 @@
         <v>6</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>4.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0353</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2636,14 +2636,14 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>0151.HK</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>32.9</v>
+        <v>30.6</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>17.9</v>
+        <v>15.6</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>15</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>6</v>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>4.8</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.0334</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2687,14 +2687,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>32.3</v>
+        <v>30.5</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>15</v>
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>0.0258</v>
+        <v>0.0281</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>1</v>
@@ -2738,14 +2738,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>EN.PA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>31.2</v>
+        <v>30.2</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>15</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>2.4</v>
@@ -2769,13 +2769,13 @@
         <v>2.1</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0.0193</v>
+        <v>0.0195</v>
       </c>
       <c r="N40" s="5" t="n">
         <v>1</v>
@@ -2789,14 +2789,14 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>0066.HK</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>31.1</v>
+        <v>30.2</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>15</v>
@@ -2808,25 +2808,25 @@
         <v>2.3</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0312</v>
+        <v>0.0195</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2856,13 +2856,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0</v>
@@ -2871,13 +2871,13 @@
         <v>2.1</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0153</v>
+        <v>0.0149</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>2.4</v>
@@ -2919,16 +2919,16 @@
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0281</v>
+        <v>0.0232</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>30.5</v>
+        <v>28.7</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2961,10 +2961,10 @@
         <v>2.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>0</v>
@@ -2973,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.0288</v>
+        <v>0.031</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>UNA.AS</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>30.3</v>
+        <v>28.4</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>15.3</v>
+        <v>13.4</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,28 +3009,28 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.018</v>
+        <v>0.0149</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,14 +3044,14 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2318.HK</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>30.2</v>
+        <v>28.3</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>15</v>
@@ -3060,28 +3060,28 @@
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0289</v>
+        <v>0.0305</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>29.2</v>
+        <v>28.3</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,13 +3111,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>3</v>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.0205</v>
+        <v>0.015</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3146,14 +3146,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>29</v>
+        <v>27.1</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>14</v>
+        <v>12.1</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>15</v>
@@ -3162,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>2.4</v>
@@ -3174,16 +3174,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0.0232</v>
+        <v>0.0237</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>1</v>
@@ -3197,14 +3197,14 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>0003.HK</t>
+          <t>0006.HK</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>28.8</v>
+        <v>26.9</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>13.8</v>
+        <v>11.9</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>15</v>
@@ -3213,13 +3213,13 @@
         <v>0</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
         <v>0</v>
@@ -3231,10 +3231,10 @@
         <v>4.8</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0214</v>
       </c>
       <c r="N49" s="8" t="n">
         <v>1</v>
@@ -3248,14 +3248,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>0762.HK</t>
+          <t>KPN.AS</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>28.7</v>
+        <v>26.4</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>15</v>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>2.4</v>
@@ -3285,7 +3285,7 @@
         <v>1.8</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0189</v>
       </c>
       <c r="N50" s="5" t="n">
         <v>1</v>
@@ -3299,14 +3299,14 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>0388.HK</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>28.2</v>
+        <v>26.4</v>
       </c>
       <c r="C51" s="8" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>15</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>2.4</v>
@@ -3333,10 +3333,10 @@
         <v>4.8</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0262</v>
       </c>
       <c r="N51" s="8" t="n">
         <v>1</v>
@@ -3350,14 +3350,14 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>6098.HK</t>
+          <t>0003.HK</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>28.2</v>
+        <v>26.4</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>13.2</v>
+        <v>11.4</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>15</v>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>0</v>
@@ -3384,10 +3384,10 @@
         <v>4.8</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0178</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>1</v>
@@ -3401,14 +3401,14 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0388.HK</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>28.1</v>
+        <v>25.8</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
       <c r="D53" s="8" t="n">
         <v>15</v>
@@ -3417,13 +3417,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G53" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>0</v>
@@ -3432,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.02</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>1</v>
@@ -3452,14 +3452,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ACA.PA</t>
+          <t>0027.HK</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>15</v>
@@ -3468,28 +3468,28 @@
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>0.0167</v>
+        <v>0.0273</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>1</v>
@@ -3503,14 +3503,14 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>0006.HK</t>
+          <t>0386.HK</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>11.9</v>
+        <v>10.8</v>
       </c>
       <c r="D55" s="8" t="n">
         <v>15</v>
@@ -3519,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0215</v>
+        <v>0.0233</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -3554,14 +3554,14 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>0066.HK</t>
+          <t>6098.HK</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>11.9</v>
+        <v>10.8</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>15</v>
@@ -3570,13 +3570,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>0.0199</v>
+        <v>0.0357</v>
       </c>
       <c r="N56" s="5" t="n">
         <v>1</v>
@@ -3605,14 +3605,14 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>0883.HK</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="D57" s="8" t="n">
         <v>15</v>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G57" s="8" t="n">
         <v>2.4</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M57" s="9" t="n">
-        <v>0.0262</v>
+        <v>0.037</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>1</v>
@@ -3656,14 +3656,14 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>0151.HK</t>
+          <t>0857.HK</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>15</v>
@@ -3672,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>0</v>
@@ -3687,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.0332</v>
+        <v>0.0364</v>
       </c>
       <c r="N58" s="5" t="n">
         <v>1</v>
@@ -3707,14 +3707,14 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>0386.HK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>15</v>
@@ -3723,28 +3723,28 @@
         <v>0</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>0.0237</v>
+        <v>0.0254</v>
       </c>
       <c r="N59" s="8" t="n">
         <v>1</v>
@@ -3758,14 +3758,14 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>0883.HK</t>
+          <t>1299.HK</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>25.7</v>
+        <v>24.5</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>15</v>
@@ -3780,7 +3780,7 @@
         <v>2.4</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
         <v>0</v>
@@ -3789,13 +3789,13 @@
         <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.0348</v>
+        <v>0.0331</v>
       </c>
       <c r="N60" s="5" t="n">
         <v>1</v>
@@ -3809,14 +3809,14 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>0857.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>10.7</v>
+        <v>7.8</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>15</v>
@@ -3825,28 +3825,28 @@
         <v>0</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.0371</v>
+        <v>0.0418</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>1</v>
@@ -3860,14 +3860,14 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>2318.HK</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
-        <v>25.1</v>
+        <v>22.2</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>10.1</v>
+        <v>7.2</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>15</v>
@@ -3876,28 +3876,28 @@
         <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0284</v>
       </c>
       <c r="N62" s="5" t="n">
         <v>1</v>
@@ -3911,14 +3911,14 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>1299.HK</t>
+          <t>0101.HK</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>24.5</v>
+        <v>22.2</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="8" t="n">
         <v>2.4</v>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>0.0355</v>
+        <v>0.0227</v>
       </c>
       <c r="N63" s="8" t="n">
         <v>1</v>
@@ -3962,14 +3962,14 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0762.HK</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>23.4</v>
+        <v>21.5</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>15</v>
@@ -3978,10 +3978,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>0</v>
@@ -3993,69 +3993,18 @@
         <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>0.0429</v>
+        <v>0.0275</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>0101.HK</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="C65" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="9" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="N65" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" s="8" t="inlineStr">
         <is>
           <t>BEAR</t>
         </is>
@@ -4176,7 +4125,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-16T22:24:40.598438</t>
+          <t>2026-06-17T05:33:47.352746</t>
         </is>
       </c>
     </row>

--- a/portfolio_report.xlsx
+++ b/portfolio_report.xlsx
@@ -1259,14 +1259,14 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>40.6</v>
+        <v>39.4</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>25.6</v>
+        <v>24.4</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>15</v>
@@ -1275,28 +1275,28 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>6</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0337</v>
+        <v>0.0205</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>1</v>
@@ -1310,14 +1310,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>15</v>
@@ -1326,28 +1326,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0239</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>1</v>
@@ -1718,14 +1718,14 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>15</v>
@@ -1734,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.0376</v>
+        <v>0.02</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>1</v>
@@ -1769,14 +1769,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>15</v>
@@ -1785,25 +1785,25 @@
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0.02</v>
@@ -1820,14 +1820,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>15</v>
@@ -1836,28 +1836,28 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.02</v>
+        <v>0.0199</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>1</v>
@@ -1871,14 +1871,14 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>15</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0.0198</v>
+        <v>0.0254</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>1</v>
@@ -1922,14 +1922,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>15</v>
@@ -1938,28 +1938,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0258</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>1</v>
@@ -1973,14 +1973,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>15</v>
@@ -1989,28 +1989,28 @@
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G25" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="M25" s="9" t="n">
-        <v>0.0258</v>
+        <v>0.0277</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>1</v>
@@ -2024,14 +2024,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>1088.HK</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>15</v>
@@ -2043,25 +2043,25 @@
         <v>2.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>6</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.0277</v>
+        <v>0.0336</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>1</v>
@@ -2075,14 +2075,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>1088.HK</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>34.1</v>
+        <v>33.4</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>15</v>
@@ -2091,28 +2091,28 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0.0336</v>
+        <v>0.0276</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>1</v>
@@ -2126,14 +2126,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>15</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>4.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0227</v>
       </c>
       <c r="N28" s="5" t="n">
         <v>1</v>
@@ -2177,14 +2177,14 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PRX.AS</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>15</v>
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>2.4</v>
@@ -2208,13 +2208,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.0344</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>1</v>
@@ -2228,14 +2228,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>PRX.AS</t>
+          <t>BN.PA</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>15</v>
@@ -2244,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>3</v>
@@ -2259,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.0344</v>
+        <v>0.0194</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>1</v>
@@ -2279,14 +2279,14 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>BN.PA</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>15</v>
@@ -2295,28 +2295,28 @@
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>0.0194</v>
+        <v>0.0288</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>1</v>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.0208</v>
+        <v>0.021</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>1</v>
@@ -2622,7 +2622,7 @@
         <v>4.8</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.0353</v>
+        <v>0.0354</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>1</v>
@@ -2673,7 +2673,7 @@
         <v>4.8</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.0334</v>
+        <v>0.0333</v>
       </c>
       <c r="N38" s="5" t="n">
         <v>1</v>
@@ -2738,7 +2738,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>0066.HK</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -2760,7 +2760,7 @@
         <v>6</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>2.1</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>0066.HK</t>
+          <t>0941.HK</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -2805,10 +2805,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         <v>2.1</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M41" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0149</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>1</v>
@@ -2840,14 +2840,14 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>0941.HK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>30.2</v>
+        <v>29</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>15</v>
@@ -2859,10 +2859,10 @@
         <v>4.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0</v>
@@ -2871,13 +2871,13 @@
         <v>2.1</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.0149</v>
+        <v>0.0232</v>
       </c>
       <c r="N42" s="5" t="n">
         <v>1</v>
@@ -2891,14 +2891,14 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>0012.HK</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>15</v>
@@ -2907,28 +2907,28 @@
         <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" s="9" t="n">
-        <v>0.0232</v>
+        <v>0.031</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>1</v>
@@ -2942,14 +2942,14 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>0012.HK</t>
+          <t>0002.HK</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>15</v>
@@ -2961,7 +2961,7 @@
         <v>2.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K44" s="5" t="n">
         <v>4.8</v>
@@ -2979,7 +2979,7 @@
         <v>1.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0.031</v>
+        <v>0.0149</v>
       </c>
       <c r="N44" s="5" t="n">
         <v>1</v>
@@ -2993,14 +2993,14 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>0002.HK</t>
+          <t>AIR.PA</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>15</v>
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>2.4</v>
@@ -3018,19 +3018,19 @@
         <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.0305</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>1</v>
@@ -3044,7 +3044,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>CS.PA</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -3063,10 +3063,10 @@
         <v>3.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>3</v>
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0.0305</v>
+        <v>0.015</v>
       </c>
       <c r="N46" s="5" t="n">
         <v>1</v>
@@ -3095,14 +3095,14 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>CS.PA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>15</v>
@@ -3111,28 +3111,28 @@
         <v>0</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.015</v>
+        <v>0.0195</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>1</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="9" t="n">
-        <v>0.0233</v>
+        <v>0.0234</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>1</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-06-17T05:33:47.352746</t>
+          <t>2026-06-17T05:37:44.466670</t>
         </is>
       </c>
     </row>
